--- a/Noticias_Calcario_20260721.xlsx
+++ b/Noticias_Calcario_20260721.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D516"/>
+  <dimension ref="A1:D513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pampa Energía vai investir US$ 2,7 bilhões na Argentina para construir uma das maiores fábricas de ureia do mundo - financenews.com.br</t>
+          <t>Crise na Mosaic: Sindicato Metabase cobra complementação salarial para trabalhadores de Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21/07/2026 10:06</t>
+          <t>21/07/2026 13:58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNSUwyaXZ0NDBMeml1X0YzN3l1TVBRRS1qRVZyVnRRSEdpNDJodGk1Mks2STR3aVZzT3pYYWhiNlN2YWVsVkJCMFRDektEck1WSHV4Y05vbWVSa0FyTXRpeFRnYUxJcWpzWW10NjRCLTMyZHZUemtZTWlKS1ExV1g4RENacGRrbjdya2FNWDFtd3BZM0Q3ZC0zaVB5dGdEWlg0bWlBVnkyNmliTFl0LWZYVGgyeXRHdk5kTnpnLTAzLWRkQXFyZWc2UDhNWVlOXzdEdklVV2FCVXczUDFsakhkNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBZWGNlWl9BREdTckFNcWVybVhfbXI4R3NvX3JuM2NCbWhrNVpMdElFTlQxNlhaV0VNZFdZM2FRWDI0VkZYWlpaRlBlbWJycjl5bVlLWlNBTnd3X1ZmMjRDOUNxRFFPdEpabnU3UXhNeVB6eHZBeEHSAXtBVV95cUxPMDktUVpCdUFuakJNbnJfTmVTU3J2NHBsSXBTZlFySXZMLTN5RGM1SHo2WHNxbjZ3SVNDbWZLdEREb1BqbmR1MzdEdzY4RWpFZV94ZU8tMnV6ZTRNaDNNc1BpeFVPc3lOM1VmQ2JXeE1fb3VkU1RZOTdIYkU?oc=5</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IMPACTOS DA GUERRA: Mosaic anuncia paralisação temporária na produção de fertilizantes em Catalão - Diante do Fato Catalão</t>
+          <t>Mercado internacional pressiona setor de fertilizantes e afeta unidade da Mosaic em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21/07/2026 09:51</t>
+          <t>21/07/2026 12:53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVXF0aWFFc2NnVDBCWFhlWk5HNHJobFgxcTJkSHNuUGhIbnhfaGd1c3l6NlVyZWtZQk5PaVg3YnFicVlxRHFULUlmY1VNc0l6WFloUnJNZkNWcWRQazYtdkxZcXJ2TlUzZjkyZXdPY1QxdVZOdTFLQXMxeWRKU3BHM3hzWllkTW4yUmZPNmw1eGhnSHI0SXRpelVqZWdNXzVhNE5rbkMzZ2tzclVZVGNwWktOX0QtRVhxQzlYQnhlZVZPZVJTUzNVSi1QVmZaVHVSRUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9sQ2F2MExzRmNzdndHMHMzblNRNHNaaXg5NDY2NXpCbkFuY24weFZpNEtXTFgzeHZzMzFrWTlVR2pkSllSdkpHR0xNNzZYbURHZ2FYRDBxcHJDMTRfTVpMZlZmZWdLcWPSAWxBVV95cUxPY2U5czZRTjNZRzNEVlBRS1ZKTlVYTDFuUjFJRFRLUXBXVExqZUkwXzZBb0FYX29qT0EydzZBMzFjSzJINWliWEFrR3ByNHdWZDNGRlROelRLX2k3M3RyTVc3T3BxWFAwUVhsLUI?oc=5</t>
         </is>
       </c>
     </row>
@@ -490,61 +490,61 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - brasilagro.com.br</t>
+          <t>Preço da ureia volta a subir no Brasil impulsionado por demanda aquecida e tensões no Oriente Médio - RCN 67</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21/07/2026 06:09</t>
+          <t>21/07/2026 12:40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQU0xaTWc1c2EwcWlLbXJ6OVpBWDZyOXc0b3hMQjYyOEpNUVFpSHpQU0FONUJLa0dHUDFQc3RPaVlkZ1BZUWNuZlk5eC1mcmUwWEY3dXV2NVNmRjZza0lMU2xZMmRtQ0FBOEpOWEV1a1lFR3FZTWpEaFZNUGhOazVUN2kyT2tYVThuR3NUZ2RlSUNBYlZXeHd2ODJUTEI5UExqT05kalMza0lDQXB0eXJmT1FR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPdzBBS2ZLOVlHZWt2eGZTajNUd092UnNMR0xWaWQ0Z2h2d1NxWWc1b3AtaTBqTWxqQ21TUjc2eXA2RXBKaWhFaklHY191X3ptcThKQ1pIR0xwcDhCUnowQXJMS0tPUktPU1pKWHBJQ054MjRZWFdIdlVGUUpyWVhmc0Y3WkZWaF9nWVMwUjgxY3ZYSnlYNVAxSzV6aEx5ZFF0aFdUREg4cEw3T0dwTzdzcDRqSjdvZUM3Zm9qRm16dlpSS2RiVHhJWG0wY0Q2WndpR2puTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
+          <t>Pampa Energía vai investir US$ 2,7 bilhões na Argentina para construir uma das maiores fábricas de ureia do mundo - financenews.com.br</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21/07/2026 06:00</t>
+          <t>21/07/2026 10:06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFAtRi1ROGFmZEZ2SWNQZmFHMnNoLUo3aFNFRTk3eXBiNVJzOXpxUmd0TVZsVVB4SWp3SDVzRlBua05KWllSc0hGQkdhX1VSbmpkX0RRd0ZrMmgzWHZxVGpxNHFYRWUyVHNfWVNKcWxjcTJzdC1IX3NzcWliX0TSAXxBVV95cUxQLUYtUThhZmRGdkljUGZhRzJzaC1KN2hTRUU5N3lwYjVSczl6cVJndE1WbFVQeElqd0g1c0ZQbmtOSlpZUnNIRkJHYV9VUm5qZF9EUXdGazJoM1h2cVRqcTRxWEVlMlRzX1lTSnFsY3Eyc3QtSF9zc3FpYl9E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNSUwyaXZ0NDBMeml1X0YzN3l1TVBRRS1qRVZyVnRRSEdpNDJodGk1Mks2STR3aVZzT3pYYWhiNlN2YWVsVkJCMFRDektEck1WSHV4Y05vbWVSa0FyTXRpeFRnYUxJcWpzWW10NjRCLTMyZHZUemtZTWlKS1ExV1g4RENacGRrbjdya2FNWDFtd3BZM0Q3ZC0zaVB5dGdEWlg0bWlBVnkyNmliTFl0LWZYVGgyeXRHdk5kTnpnLTAzLWRkQXFyZWc2UDhNWVlOXzdEdklVV2FCVXczUDFsakhkNQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
+          <t>IMPACTOS DA GUERRA: Mosaic anuncia paralisação temporária na produção de fertilizantes em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20/07/2026 17:29</t>
+          <t>21/07/2026 09:51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVXF0aWFFc2NnVDBCWFhlWk5HNHJobFgxcTJkSHNuUGhIbnhfaGd1c3l6NlVyZWtZQk5PaVg3YnFicVlxRHFULUlmY1VNc0l6WFloUnJNZkNWcWRQazYtdkxZcXJ2TlUzZjkyZXdPY1QxdVZOdTFLQXMxeWRKU3BHM3hzWllkTW4yUmZPNmw1eGhnSHI0SXRpelVqZWdNXzVhNE5rbkMzZ2tzclVZVGNwWktOX0QtRVhxQzlYQnhlZVZPZVJTUzNVSi1QVmZaVHVSRUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tensão geopolítica impulsiona alta da ureia, avalia StoneX - Revista Cultivar</t>
+          <t>Argentina investe US$ 1 bi em fábrica de ureia de olho no Brasil - - Misto Brasil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20/07/2026 17:06</t>
+          <t>21/07/2026 09:31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRTFaSlhVS2VHUElxU1duN3ZDRVRYYWcweWN4MG1nY1RUYWQ4bkVmeFQ0Tld6RW9jZWJOSmFVOFUwdFJpWVFRelF0WVV1ZGIwczYycWpxN1VvdkJzSGhyd1doYm52bF9FVVoxQ0hhcGRlT3h3bHpwVGVBNWNfTDlDQWxQd0V4WHNRemNDT2o0eXh4X3V0TF8zNGtyS3NuUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcVhqd0VYV3hZUEhWang1YWNxZE5Nbkh1N1BjNkRNckZVVV9TU19va3JlbGw5dE5ySFQzMkxwaUFDdldGVzVMYk15VlNORE9ESWJFY1cxNDdBdnZ5R2NHYU5jVV9NLTlSemJfTE9tOE1wNEt1M2ZQclZmdWtzcDIyWDluQmhmT09qUHBRdXVBa0dEUmlSTjZCOVdWbVExTVRJ0gGoAUFVX3lxTE1XcXBpeXU5UkV0UmVZSk9QMWlwN0d6VWJsbFBKQWhMd28wa2JqbkJmT09mdG1Fdnp6SXp4Z3pUaFFpWXR2UVZFQUt3YkF6cE0xM2tVOUlodTU5TzdfWUxvNWtnQkNTUUxDOGg5Q0luWEptWThhY1NXYVBPNllaZEpkdi14M19hWTlzZER4UTVSVGJQZDFqSm56QkIyN3VicTVyS1Q2ZWZqdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -578,39 +578,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
+          <t>Ureia valoriza mais de 18% em um mês puxada por demanda e geopolítica - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20/07/2026 16:28</t>
+          <t>21/07/2026 06:09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQU0xaTWc1c2EwcWlLbXJ6OVpBWDZyOXc0b3hMQjYyOEpNUVFpSHpQU0FONUJLa0dHUDFQc3RPaVlkZ1BZUWNuZlk5eC1mcmUwWEY3dXV2NVNmRjZza0lMU2xZMmRtQ0FBOEpOWEV1a1lFR3FZTWpEaFZNUGhOazVUN2kyT2tYVThuR3NUZ2RlSUNBYlZXeHd2ODJUTEI5UExqT05kalMza0lDQXB0eXJmT1FR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ureia sobe com retomada da demanda e tensões no Oriente Médio - StoneX</t>
+          <t>Às vésperas da safra mais valiosa do Brasil, uma multinacional redesenha a oferta de fertilizantes - InvestNews</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20/07/2026 14:55</t>
+          <t>21/07/2026 06:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdVlYMDZsdXIycGJycGFsS2lBVlliVThkYVZNRi1qSUlmRjZQeG1XN05Fc0JvcHB0QmtOVmV4WEhGbk51OWFyODZqblZwXzVOMlBuUWJjSHZtUDZxeUtyT2VBUmgxSjRxanRUNnRaSmJhQ2RoUjdlYmhjWC00Njl1LXItczhoMWd4ZkFFUlJMVVdWZG1WdE04Y240RV9HRlcyMGNybDJZQXBlUHpkU3Z0Zjg4b3ZuanVROVdnaGxLcUtTZFZiQXUwZS05Mm13MkNCdG1HSHpEdWtDOUVWNW01TGI3UEdIdGxwRmg1aEowZThtTVdKUGdoUV81THVLRG9kcUozR2MzWFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFAtRi1ROGFmZEZ2SWNQZmFHMnNoLUo3aFNFRTk3eXBiNVJzOXpxUmd0TVZsVVB4SWp3SDVzRlBua05KWllSc0hGQkdhX1VSbmpkX0RRd0ZrMmgzWHZxVGpxNHFYRWUyVHNfWVNKcWxjcTJzdC1IX3NzcWliX0TSAXxBVV95cUxQLUYtUThhZmRGdkljUGZhRzJzaC1KN2hTRUU5N3lwYjVSczl6cVJndE1WbFVQeElqd0g1c0ZQbmtOSlpZUnNIRkJHYV9VUm5qZF9EUXdGazJoM1h2cVRqcTRxWEVlMlRzX1lTSnFsY3Eyc3QtSF9zc3FpYl9E?oc=5</t>
         </is>
       </c>
     </row>
@@ -622,83 +622,83 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aumento no preço da ureia reflete tensões no Oriente Médio - boca.com.br</t>
+          <t>Pampa Energía confirma nova fábrica de ureia de US$ 2,7 bi que mira o Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20/07/2026 14:30</t>
+          <t>20/07/2026 17:29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPYVplQThxbmkzVGFWT0hpUTB0SnU1dGlNOXZlQ0FNaGdkRXdjRXhRTUFBMVZFSl9HcTRvY3hKWllNVnFTRzdPOWZaVFM2OTFNSDZ4YnZuVW0wRjNGVGFCYlItVk51bGFNbjBJZmRwb2pQRklVMHhmYmwxeW42bXB0akhadTEzU3J3N2NoYlBTQmxnWFpE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPeFZEM0NBMDFsS3ZfN1VJTDE1ZjJ3bGZMcG9qVUgtNjhWb0VxODFEUHhkRHFJZ2w0RmZEbDJSNFI5VXV2OE5IR1RRTTZWVXZSUVg1SFBmbXRxYkl6czNqWU1BRS1LWFROQUJlcjdybEQ3SmFDb0NKMDk2ZFkxb193NzFuOGh0YTJJUUtrTmR1MmotcGNZSDBJdDZRdDNEOVpaQ1lSU0duRm1BblF2NFB3aWZqR1dnb1EyRWp0X1NnVVp2TC1fcjNtenVB0gHYAUFVX3lxTE1rRjEwOVdRaURTMDIyNnpHR09ydml4SnlSdVl3MnFBOHMxR0RsMUxGYzNMMjVBYzJ2OVRuWG1HbjNMRnRfZzRmSUUxbzgzcHJacFNSWXdIemdxd3daSDBMWnQ5OHc4OUJRN2kzdW02X19xeWpPRUREc2taYkY0RmNCUkRlYnRuVG9vdkFnNUEzYlUwR3FtR2MyWVFJOVRBYzktcTVCdVZGM3FYUVVyd0FrYzJwb3lvcjJvc2M0cWJaMG51VERCVHlNNXVjc3lnOFJ2aFg0VHBmbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Galeria de Revestimientos porcelánicos de gran formato - XLIGHT - 5 - ArchDaily</t>
+          <t>Tensão geopolítica impulsiona alta da ureia, avalia StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20/07/2026 14:17</t>
+          <t>20/07/2026 17:06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPOEZPaWxndHVBc09GcFlvbnU3THJYcWV3VDhQdFk1NDNzLVF2Ynl5Qmc0bllzdTRpMm1NOVJYT3lsZERRanl0RDNTUWxzRWUxRmRoMUgxQWlCU3hlckstWFhpb3lzTHlfVnJCTWU4NEh6d3FsQ3diZm80MFdta0RKcnV1ZWkxOWE3bXgzTGdfaG5CVEVhem1kWnVOeHM5YXFXNWI2am5sSTdrZmZXemRLaGpZZlRaX2xCSWRYRjNmSzlJTUlsdDFiTzNndHR2bTJtemcwRUhONFV3dnJUM3M2S3dLZWlKbEFJZTZhRXpJaHBJdm5LbFU1RkZ2RWVfZVVhbUEzQ3JZTDB6cnJSU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPRTFaSlhVS2VHUElxU1duN3ZDRVRYYWcweWN4MG1nY1RUYWQ4bkVmeFQ0Tld6RW9jZWJOSmFVOFUwdFJpWVFRelF0WVV1ZGIwczYycWpxN1VvdkJzSGhyd1doYm52bF9FVVoxQ0hhcGRlT3h3bHpwVGVBNWNfTDlDQWxQd0V4WHNRemNDT2o0eXh4X3V0TF8zNGtyS3NuUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Escassez de enxofre fecha fábricas, ameaça oferta de adubo e pressiona custos do agronegócio brasileiro - JBNEWS</t>
+          <t>Cotações da ureia voltam a ganhar força e acumulam três semanas de alta - Globo Rural</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20/07/2026 13:41</t>
+          <t>20/07/2026 16:28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3FIWUJOeFVabjdUd3VBS2FRV29fQlpNaURDU3ZpdlB2b2UwNnpreFF5aFg1Z3g4TmM0bmRmZkJRNHUyTjg5dFhZLTVDMEE2b3RHdi16aUJnVUpnYVlodEVFRUg0b3lYUFVwU1lNVy1sX1lreVJ4WnRLOG1SODVuUW95ZkZyQm5WOXhPNXF1VTR5S21DVEdJZ3dZWVVETFNESlRBTVZyd1NDNEhXbzN6cXdha2RISVhIVVJSeS1peWNRZlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPNE43X3FKaDhjVWxiYmRWTGNFb2kyU0hka3lSbzVjQllEVXBmRVh6N3UxdVREQlREYS1fb2wzNTNjcF9BRnI1QU1ZX0VBSDBKRWp1SXo4dkU5ZFdreHJJNVZ4bTNOM1V3ZjJieTFxQnpQSm9wWTJjUmlpU3Y0YXhlamItUmx4MnZuckNBTF8xbWtvQ25VWGo4dVdST1JhS2tWR0MtNHY2XzQ4d1ByUHo1ak5BS0xrZFRRaUlpbWFERnNXV29PS1VLMzNR0gHYAUFVX3lxTE5FeHdzOEpTZzVPeWhxeEhIbGlQMVJiejdsMGlxRnlDcU1vSDhhcXJTcGVDWmtqc0NsTXUwWGhtVzNhLXNZbFhncWc3cWhJZWxaUFpJZ21DTkNZT3p3eVR2aUEzcEFVUkZ4S0QwbEwydmJ6R2tVX2tVUWtXVm1VbVgwX2Y0TkQ5cFB0WWduTWZxcVJwOHc5SzJXSi1PWnV5QUt0LWI4X1ZpVlh2UUo0Zm5udWhzYTl1MXRxOWtwZ1cwVmJUUVRTZFpGc0dmQ0VHZUtKeVFsUjFBNQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
+          <t>Ureia sobe com retomada da demanda e tensões no Oriente Médio - StoneX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20/07/2026 12:29</t>
+          <t>20/07/2026 14:55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdVlYMDZsdXIycGJycGFsS2lBVlliVThkYVZNRi1qSUlmRjZQeG1XN05Fc0JvcHB0QmtOVmV4WEhGbk51OWFyODZqblZwXzVOMlBuUWJjSHZtUDZxeUtyT2VBUmgxSjRxanRUNnRaSmJhQ2RoUjdlYmhjWC00Njl1LXItczhoMWd4ZkFFUlJMVVdWZG1WdE04Y240RV9HRlcyMGNybDJZQXBlUHpkU3Z0Zjg4b3ZuanVROVdnaGxLcUtTZFZiQXUwZS05Mm13MkNCdG1HSHpEdWtDOUVWNW01TGI3UEdIdGxwRmg1aEowZThtTVdKUGdoUV81THVLRG9kcUozR2MzWFk?oc=5</t>
         </is>
       </c>
     </row>
@@ -710,105 +710,105 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fertilizantes: queda da ureia muda estratégia de compra para a safrinha, enquanto fosfatados seguem pressionados - Portal do Agronegócio</t>
+          <t>Aumento no preço da ureia reflete tensões no Oriente Médio - boca.com.br</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20/07/2026 11:54</t>
+          <t>20/07/2026 14:30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOMHRNQ2NnOGdncUVqdnhHZzEwMEJwTXZESFNRTGVKc2pqT1htMDlZMmRINWZxUy0tbURDUGJsVEs2M1psdEFIR1cxcEpCalhxd2JoNmpFQ1RiWWFINnlLbTRKbWtHbmNvdEFadGltS0plRk5DdjJoaW1oaGY5S1ZNN0tDaGRocHUzRHVlQk9oWkhFRWRYaXV5NmN1RnI5ZmFjYU53UVd6UTROcms1akhMejVRYkpJM3l6eWl0bUlPd1cza01NaGlKQVFQbEhsdkltZEJLUjQ3bnppdGpZMkVSRkRqUzVBMjhYbDdpR2lNeUFhZGxvUzhhSl91Tmo4YWVtaUU2dkZzRElEQUtRenNaanVXRldSVGhXem5CWHJXaHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPYVplQThxbmkzVGFWT0hpUTB0SnU1dGlNOXZlQ0FNaGdkRXdjRXhRTUFBMVZFSl9HcTRvY3hKWllNVnFTRzdPOWZaVFM2OTFNSDZ4YnZuVW0wRjNGVGFCYlItVk51bGFNbjBJZmRwb2pQRklVMHhmYmwxeW42bXB0akhadTEzU3J3N2NoYlBTQmxnWFpE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
+          <t>Galeria de Revestimientos porcelánicos de gran formato - XLIGHT - 9 - ArchDaily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20/07/2026 11:24</t>
+          <t>20/07/2026 14:17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPZXpXV3o4TnowbVJ1T3RPTVRSQW1MQ3QtR2JNODRvTUxOSXNvOFAzLVl2TVpOSXE1elBxR0NCOFczcjNzRzloOFVxT3B6M1FZRmNLTFhKcXlqLVlCNFdZWHdlOFM1eHZmcFhfMHQwdEJNSEVUQ2JISjFrRG52R3FTMnpVR1dQazVpQWN4aVRnUDNsSTk0d25Xa3dVWUlvaC1LcC1aQ2tNSjZxQ2xKdzI2OWdTWmxTSTZBUlRTU2g1SGVlZ0U0dmNiUEsyc1lvWXFDMVdWOUFWUmk1SUczUFhwcGdpdmg4dmZhY09zZ25RblZjN3NWeGtrRGEwWXR1Mzcxb1dhdC1Zai1kUXZhR0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Segunda-feira 20 de Julho de 2026 - RRMAIS</t>
+          <t>Escassez de enxofre fecha fábricas, ameaça oferta de adubo e pressiona custos do agronegócio brasileiro - JBNEWS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20/07/2026 10:55</t>
+          <t>20/07/2026 13:41</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTFNselBTQzRUNjBiZlAxdXZBeDVOU3FoVVNZVDUxQU9ING1qbThzNk9rMmZ0elduWnhBOFhYN09IMlpZS0J3WTAyX1ZnN1plTVV2eEVmSDJzZHRkSWh2ZUlEbFVJLVJFaGc4N19CNGdscENfSkc5WHVVNUlTeU4xeVY0c3V0THRkWWVwSEJvcXpHQ3l0emV4M3gwd185QnBTeWJldTNFWjU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQa3FIWUJOeFVabjdUd3VBS2FRV29fQlpNaURDU3ZpdlB2b2UwNnpreFF5aFg1Z3g4TmM0bmRmZkJRNHUyTjg5dFhZLTVDMEE2b3RHdi16aUJnVUpnYVlodEVFRUg0b3lYUFVwU1lNVy1sX1lreVJ4WnRLOG1SODVuUW95ZkZyQm5WOXhPNXF1VTR5S21DVEdJZ3dZWVVETFNESlRBTVZyd1NDNEhXbzN6cXdha2RISVhIVVJSeS1peWNRZlk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Espanha x Argentina: adolescente morre durante festejos do título mundial - Diário do Distrito</t>
+          <t>Mosaic paralisa produção em Catalão por falta de enxofre e sindicato teme impacto em 650 empregos - Diário de Goiás</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20/07/2026 09:07</t>
+          <t>20/07/2026 12:29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNako0UEZyc1FyLTVDbzU4N3BYdng1eE1wa3ZaZEo5dmh3S3JkSDZqTDZMVnJGeGRLbWl4aS1HQzE1ek9FN2t1b2J6bDk0dTdxYU00ZTVJV3NUaEFRdnVKazY2TXBfdDdmVmRkSHVGOXhyV0Fnc0RMSHo4bTQwN3ViMVBqTkJIZ0xMZE1va3QzMlNhcjhRa0tXanhjVUFrTl9DdEV4UUVlTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNend4a0d3ZVRsdjhtTWlXRWhJQTBlSXFEdjNYX1ZpcElMY0FiUzUySmM1dzQ3TmJwOHhYeGF1eE1jYXYyUXhvWVVOUDdoT05keEg3QmFZbHpzZVByVG4zLV9VZnVHNlYyTHhUUTVoVFB2UlNQWHVXNElsV2N1MjRlVUxLNVhadGRucjB4LURtdXJWSHRPem1QYmFDNVVrNXFTMUFuNkdlMVhyU3pLRmFUV2VvYU1YVWpZLTVMY2pHNDlKTTJXTE81YmtfdVlHVDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
+          <t>Fertilizantes: queda da ureia muda estratégia de compra para a safrinha, enquanto fosfatados seguem pressionados - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20/07/2026 03:43</t>
+          <t>20/07/2026 11:54</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f9c54f431497f7cfa156c825bb&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxOMHRNQ2NnOGdncUVqdnhHZzEwMEJwTXZESFNRTGVKc2pqT1htMDlZMmRINWZxUy0tbURDUGJsVEs2M1psdEFIR1cxcEpCalhxd2JoNmpFQ1RiWWFINnlLbTRKbWtHbmNvdEFadGltS0plRk5DdjJoaW1oaGY5S1ZNN0tDaGRocHUzRHVlQk9oWkhFRWRYaXV5NmN1RnI5ZmFjYU53UVd6UTROcms1akhMejVRYkpJM3l6eWl0bUlPd1cza01NaGlKQVFQbEhsdkltZEJLUjQ3bnppdGpZMkVSRkRqUzVBMjhYbDdpR2lNeUFhZGxvUzhhSl91Tmo4YWVtaUU2dkZzRElEQUtRenNaanVXRldSVGhXem5CWHJXaHY?oc=5</t>
         </is>
       </c>
     </row>
@@ -820,83 +820,83 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
+          <t>Da guerra no Oriente Médio à Mosaic: entenda por que empregos estão em risco em Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19/07/2026 22:37</t>
+          <t>20/07/2026 11:33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNbHZvTzRTZHlrTHpsQmFFV0k2Qi0wWTh1SXhHN0pvcDgwUzVHRGFVVzc4bXNSeHJLRGlwQzkzRWxtYVJERFBReVlRaC1paTNIRHN0YWVhc0QxQnJyaXBrdzhqeWdtSzZ6Vk1jaU9SZ0VNMkc3UHg0YlRVdmtFNVZWT0tybTdRUm9STWt4SlBKM0ktLXZ2SVRtb3ZYaC1ZV2VSQ0NqMWoyVmROQUVBNDNyazNmLTFvc3l3M2JzWDlKUHlaUmdM0gHMAUFVX3lxTE1qQkF4YVY1VXNFRjdHSllUaTJOM0c2V3V4Y1dYYWJyWmFDOXlJWXZVaEd1MWxhS185REZyc3owaHA5NjlrSzNSdC0wc3hzOXBkQ2xrMnRPcFZ6ZUFHYXlxcDQ4eUxBSU12Z2luVVNFRVMyRGx6SnJxeXVwQmhKT0FSODNWZVVPekNqVlM4aUVWSE5iTHRiRHl6RklWMkRGTXQzVW5YN1VBS0YtUERfeWlLX3hsNk1nZGJUc3diRTBqZ3ZLWmNjMWpKNWkxQw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
+          <t>Cotações Agrícolas para esta Segunda-feira 20 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19/07/2026 16:20</t>
+          <t>20/07/2026 10:55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTFNselBTQzRUNjBiZlAxdXZBeDVOU3FoVVNZVDUxQU9ING1qbThzNk9rMmZ0elduWnhBOFhYN09IMlpZS0J3WTAyX1ZnN1plTVV2eEVmSDJzZHRkSWh2ZUlEbFVJLVJFaGc4N19CNGdscENfSkc5WHVVNUlTeU4xeVY0c3V0THRkWWVwSEJvcXpHQ3l0emV4M3gwd185QnBTeWJldTNFWjU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
+          <t>Espanha x Argentina: adolescente morre durante festejos do título mundial - Diário do Distrito</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19/07/2026 12:04</t>
+          <t>20/07/2026 09:07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwNBVV95cUxQVVNGS0NQLTlRalJSNlBDX0w1bE9Fa0V6U21pV3ppN2hCcXR3dmdPaHk0OURTaHZtMC1JRHI2Nk5kc1lnUjNVQW5WSGY1LW00V0JHM2tPNUotU3phNU9rWTNyR09PMlpSWXVaMU1lemxSdzBsbkczWXdtSkcwcENlLXhhZFM2MVdGVW4zT0R1aVI0VDVMdVU3X0dEMUV6UnkwQjZsYUVEcjFPRGFyUHRnc3J1R0ZWMnd2Vm1oU3l5R2ZrbTYyRWNvUGlzTFRCRnZocXlDWGF5RmFHdHo4N1ZJZ2ZqYjZMOHV6ZExRTW9UQUpndFN6NW1qTi1lSGZhVHZjb1NvX2pKN29OYm5RN09jNEdJZmxTbFM0cVZreENmbWZoTWRoemw5NXpYLXZlWUIzZ240NzN1dG9OZ1B4cVI2YS1pMGstY05IOVYxSHp3UXE0bXd0RDIwN21pU3FTYVEwTWdUMjB2M0RCTWg4UXRvT09tTHZtNWloNU1kSFNUeFFieTRqZDdjTWhOYm03NDZJRzVSVkphWWtQYko1VUxDQ0QwVmNZZTFUc29wR2xnQ2gxb0dHdm5JanJmOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNako0UEZyc1FyLTVDbzU4N3BYdng1eE1wa3ZaZEo5dmh3S3JkSDZqTDZMVnJGeGRLbWl4aS1HQzE1ek9FN2t1b2J6bDk0dTdxYU00ZTVJV3NUaEFRdnVKazY2TXBfdDdmVmRkSHVGOXhyV0Fnc0RMSHo4bTQwN3ViMVBqTkJIZ0xMZE1va3QzMlNhcjhRa0tXanhjVUFrTl9DdEV4UUVlTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Proteína ajusta defesa vegetal à oferta de enxofre - Revista Cultivar</t>
+          <t>Murang'a county distributes lime to coffee farmers to boost production</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19/07/2026 09:40</t>
+          <t>20/07/2026 03:43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVGlUQzZ6UDhYaDg3ZUNHTEwwbDBZcTlnVUVGUTFkalFpLUpQSVRnSTZCOVFYcGlub0FBSWNSTGE2WEFfS0ZpdFNnZGZyU3hick90QmF2WmpIUWNYVVNqajhBVUZSREF3UVJtMzJKT25sVTZkVU1UQzhZR0VENFdMRTVfRU10dTNOSllMdHlraGllX056?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab2a48a4a969f7eaa51f2defde0&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -908,39 +908,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles in L'Atelier Patisserie Bathroom - 4 - ArchDaily</t>
+          <t>Mosaic pode demitir mais 650 trabalhadores em Catalão - O Popular</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19/07/2026 03:13</t>
+          <t>19/07/2026 22:37</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQNVE0N1J5cjkzSjg5SHBaVjZhU1VUOFpES0o1SFlIRTNTanlrRl8zdmtZODJhUV9DLVRERXNVeWt3YUZOMTVqSEtlVTlBWXJhZF9BQ0JyTUpub2YtQ2JIRDRvSEFPYTZGeXFfU1JuQkxZOGRLLWlSSi1zZ25pM3N4NTVKSUpBZ0tXZlQ4LUNWdkd2WlZ6anZDZFRTdkNmYmh0d1Z3bzNBd09ZR0VNbG1XR0lmRGRGVHJoamtVSUFmdlNwMC0yTzlVT2NvdTBjZFNma1VRWGJJOUR5RHJ3LTJKV05MVGF3aDAyX2V0QnRqNDYteTFudzJoNENfeXh1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWC0wUm16Y1hGUHdCR2JRdnhOT0JyM3UxQ2tlVndJQVhDVWw5cU1WdlNIWnpFdzVpNDlrb294TFB5MERjbnZrZVpOOVMyOUtwRXZVNWJoakRQYlc2Z1lwYV9RaFhBbTZ2WFFnc2E0LTZ4UXg0NlFvVHB4c0JPQ0czam5YdTEwRmlqVnEtUi0tOC1MOFRtaWh1MW9zTHA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 8 - ArchDaily</t>
+          <t>Ergueram pilares de calcário de até 5,5 metros há 11.500 anos, quando a agricultura ainda começava a transformar a vida humana - Revista Oeste</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18/07/2026 21:52</t>
+          <t>19/07/2026 16:20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQV0JMRWxtTFRtQUxyejdKTmZzUjAteGkyQzl2MDBiQkRKdUxkMUlwN3R2OWFfUkhidnczdEJKZkdGTmMwSEhqVjcwZ1lmWWZVU0JOR0tMcGFoSUZ1Y3VsR3JrZFloLXJ3Uk9IYXJRRlRsNHMtNkNFMElDb1dlM19TQXdrYkF6TURlOXptQzFVS2c3WDZIRGxJeUVHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQMHFxcXZoN2VHVEtqVWMtMXR0Tm5RX2dqZnJsT21XZUJnRW1qX0h2dUxoNzcyUUZGQ2ZvY1Fzd0lsTlk3MDdVMnBTSk5jbGJfY2VRSGFScnoyS0dybGlpME1odk9ZdGJSV3lNUkN5VUItTHZUdGVObFV2R01UbzZGUXRMUl9iMVB1LUh4X2JTZU9fSjA5aW04bHI5YldvT1Q1NFpsZFkyRGRQQTgzVko4elVBODRsbWhTeXdpVFRjX195WTE5NVFOclNBV0VOSmVLRG5IZlk2NWtuMEFkVTMzYVB2aHBwb2NpTkw1dGxWbkdLa2loekxXS0J4NjBMemhSUkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -952,61 +952,61 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Terra - 1 - ArchDaily</t>
+          <t>Guerra no Irã: empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18/07/2026 20:16</t>
+          <t>19/07/2026 12:04</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOa2Y4R1VBS3NJRDhtM2RhOUFBNE5EN2Y2bjBsOVJwSFZweE8wSExrYnZVUGtnRkU3czZ2WWppeGtob0M0SldGSXBXdlVYeVZWck9sWU80TmxLQkNEVWZfVjhuQWRvUkV4ZlAzUlN1S1hZbll4dEJUSDJoS2hNQzd2Y0h3WXgtMlF2RjRuS2dBdFBmZjAxazV5eFhZNU5wLUJRY3piTG5jZnEwS3BZZExtMDJ5WEFkUjNidjRnU2p5WHRCdllTVS1mRUU3MDN3MldyeTB2OVd6N1NoeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwNBVV95cUxQVVNGS0NQLTlRalJSNlBDX0w1bE9Fa0V6U21pV3ppN2hCcXR3dmdPaHk0OURTaHZtMC1JRHI2Nk5kc1lnUjNVQW5WSGY1LW00V0JHM2tPNUotU3phNU9rWTNyR09PMlpSWXVaMU1lemxSdzBsbkczWXdtSkcwcENlLXhhZFM2MVdGVW4zT0R1aVI0VDVMdVU3X0dEMUV6UnkwQjZsYUVEcjFPRGFyUHRnc3J1R0ZWMnd2Vm1oU3l5R2ZrbTYyRWNvUGlzTFRCRnZocXlDWGF5RmFHdHo4N1ZJZ2ZqYjZMOHV6ZExRTW9UQUpndFN6NW1qTi1lSGZhVHZjb1NvX2pKN29OYm5RN09jNEdJZmxTbFM0cVZreENmbWZoTWRoemw5NXpYLXZlWUIzZ240NzN1dG9OZ1B4cVI2YS1pMGstY05IOVYxSHp3UXE0bXd0RDIwN21pU3FTYVEwTWdUMjB2M0RCTWg4UXRvT09tTHZtNWloNU1kSFNUeFFieTRqZDdjTWhOYm03NDZJRzVSVkphWWtQYko1VUxDQ0QwVmNZZTFUc29wR2xnQ2gxb0dHdm5JanJmOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Aqualuxe - 4 - ArchDaily</t>
+          <t>Proteína ajusta defesa vegetal à oferta de enxofre - Revista Cultivar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18/07/2026 13:49</t>
+          <t>19/07/2026 09:40</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnBnX1FxQ2lyT3U3bGFrTzBXMTZJNlV4MjhYT2tFUlpkYm5za1NlQTNKZXd4R21RUi11My1xVzNrRzZ5RzNEcDUxV0wwMnRxcFBha0ZZOTFzMnpwZ2kwNTRTbGttTGc3bUMwSkQxYTZMN2l5SmdYTG9DRUp3QU1VRVc2SURDY3BSUkNkWVJjSUY4ZjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVGlUQzZ6UDhYaDg3ZUNHTEwwbDBZcTlnVUVGUTFkalFpLUpQSVRnSTZCOVFYcGlub0FBSWNSTGE2WEFfS0ZpdFNnZGZyU3hick90QmF2WmpIUWNYVVNqajhBVUZSREF3UVJtMzJKT25sVTZkVU1UQzhZR0VENFdMRTVfRU10dTNOSllMdHlraGllX056?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
+          <t>Galeria de Mosaic Tiles in L'Atelier Patisserie Bathroom - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18/07/2026 12:05</t>
+          <t>19/07/2026 03:13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQNVE0N1J5cjkzSjg5SHBaVjZhU1VUOFpES0o1SFlIRTNTanlrRl8zdmtZODJhUV9DLVRERXNVeWt3YUZOMTVqSEtlVTlBWXJhZF9BQ0JyTUpub2YtQ2JIRDRvSEFPYTZGeXFfU1JuQkxZOGRLLWlSSi1zZ25pM3N4NTVKSUpBZ0tXZlQ4LUNWdkd2WlZ6anZDZFRTdkNmYmh0d1Z3bzNBd09ZR0VNbG1XR0lmRGRGVHJoamtVSUFmdlNwMC0yTzlVT2NvdTBjZFNma1VRWGJJOUR5RHJ3LTJKV05MVGF3aDAyX2V0QnRqNDYteTFudzJoNENfeXh1dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 4 - ArchDaily</t>
+          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18/07/2026 09:50</t>
+          <t>18/07/2026 21:52</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOC1mRGd5Nzk0UjdlY0NRNHlsb3ZtNk5DYTBNbHhaVU1GTlNzTnFMZXFYWnBwNllGbmd1RGhuVmlMNjZkeXRYVHFxM0dld2JwTVBjTWtZTTVLVW1CSHYzLW1qeHdhX2swM2dyVGxlSTJiS2prYmZmVlRUQXEyMXYydk9MTWJEcklTQ1dteEF5SEpqc21HTDdsY2xoM3NMV2JBVmpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQV0JMRWxtTFRtQUxyejdKTmZzUjAteGkyQzl2MDBiQkRKdUxkMUlwN3R2OWFfUkhidnczdEJKZkdGTmMwSEhqVjcwZ1lmWWZVU0JOR0tMcGFoSUZ1Y3VsR3JrZFloLXJ3Uk9IYXJRRlRsNHMtNkNFMElDb1dlM19TQXdrYkF6TURlOXptQzFVS2c3WDZIRGxJeUVHSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1040,83 +1040,83 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Niebla Swimming Pools - 5 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Terra - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18/07/2026 01:45</t>
+          <t>18/07/2026 20:16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSFVHMV9GYzJhZzh6Vnh6cEduLUFIcW9JM0liMEdGV1ZsOUdCMmpQWDNFaWlWRnZpUUQ3TjhwVTQ4UkRrZk9WY3JfeXpFMVQ3U1F3aUh0ZUNIOXlsdGFpTldJXzh3dmc3dHIza21iV0laZmhNbTUzUDFWbkxMdU5tRndxQnVCZVU1SjF4Z3VPNm5BMjRoR0lTTmlXbFpjZGhHM0V2YlBfZGEzMUlmOU9wdFp2NFBBSHBZS2w1UDZoUmwtMWJ5RjZXdXh6MV9mYUpsYnB1V19FclFnUjNSSmx5bW9CaldBSFhOVjJ5UW1zLTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOa2Y4R1VBS3NJRDhtM2RhOUFBNE5EN2Y2bjBsOVJwSFZweE8wSExrYnZVUGtnRkU3czZ2WWppeGtob0M0SldGSXBXdlVYeVZWck9sWU80TmxLQkNEVWZfVjhuQWRvUkV4ZlAzUlN1S1hZbll4dEJUSDJoS2hNQzd2Y0h3WXgtMlF2RjRuS2dBdFBmZjAxazV5eFhZNU5wLUJRY3piTG5jZnEwS3BZZExtMDJ5WEFkUjNidjRnU2p5WHRCdllTVS1mRUU3MDN3MldyeTB2OVd6N1NoeXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Aqualuxe - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18/07/2026 01:44</t>
+          <t>18/07/2026 13:49</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnBnX1FxQ2lyT3U3bGFrTzBXMTZJNlV4MjhYT2tFUlpkYm5za1NlQTNKZXd4R21RUi11My1xVzNrRzZ5RzNEcDUxV0wwMnRxcFBha0ZZOTFzMnpwZ2kwNTRTbGttTGc3bUMwSkQxYTZMN2l5SmdYTG9DRUp3QU1VRVc2SURDY3BSUkNkWVJjSUY4ZjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Through the Seven Seas - 4 - ArchDaily</t>
+          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18/07/2026 00:46</t>
+          <t>18/07/2026 12:05</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWXJZMk5remlBSFU4WEY0TEtEcDhQNXVvRm9KemsyakoxYWpOU2pHdFdCUzg2SXdMc09MVkRVdlZ0VTV4TGY0anlPUG9KZmpla28wRlJDY3RqbVNvMEhQY0xyUG8zeWp2WjdZY19GNzFOV19MQjA5WUwxb1ZEbkhVQVc5LXEtQ0lNSk91N1hpczhVTDNBRDlPT25PczQwTTlvMzhfYWhwZVRxUWJEdWJNM0ctSGxaU2xSdHE3STdkdDZTcUk2dWJFdlJRMmFDUU5TbXZ5WDNLOEhqVzdEODhkX0hfYnpUQXlfUncwUllFbjlxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles in Barcelona Private Flat - 2 - ArchDaily</t>
+          <t>Galeria de Limestone, Granite and Travertine - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18/07/2026 00:18</t>
+          <t>18/07/2026 09:50</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPY0xjMER6TGxTeHlsbTN1aVp1d2VSUnBtSVdsdDFYT1gxTmphd2xhc1lEeUtJdkdZdXZfcGZLeW9NYkZDd2xfdEd2M3UxbmtiTWxXRFFOTmdld0xnRnh1TWRjc3lXcEhpRkdsZDYyU3dZZXFyWWV2S2VDbDNIbGJVTFpZZmxGTHFRWWp3cXBIcUhBbnZCRl9hOFROM1JRck02NlJ4ZFNQSklGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOC1mRGd5Nzk0UjdlY0NRNHlsb3ZtNk5DYTBNbHhaVU1GTlNzTnFMZXFYWnBwNllGbmd1RGhuVmlMNjZkeXRYVHFxM0dld2JwTVBjTWtZTTVLVW1CSHYzLW1qeHdhX2swM2dyVGxlSTJiS2prYmZmVlRUQXEyMXYydk9MTWJEcklTQ1dteEF5SEpqc21HTDdsY2xoM3NMV2JBVmpJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1128,39 +1128,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
+          <t>Galeria de Mosaic Tiles - Niebla Swimming Pools - 5 - ArchDaily</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17/07/2026 20:47</t>
+          <t>18/07/2026 01:45</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOSFVHMV9GYzJhZzh6Vnh6cEduLUFIcW9JM0liMEdGV1ZsOUdCMmpQWDNFaWlWRnZpUUQ3TjhwVTQ4UkRrZk9WY3JfeXpFMVQ3U1F3aUh0ZUNIOXlsdGFpTldJXzh3dmc3dHIza21iV0laZmhNbTUzUDFWbkxMdU5tRndxQnVCZVU1SjF4Z3VPNm5BMjRoR0lTTmlXbFpjZGhHM0V2YlBfZGEzMUlmOU9wdFp2NFBBSHBZS2w1UDZoUmwtMWJ5RjZXdXh6MV9mYUpsYnB1V19FclFnUjNSSmx5bW9CaldBSFhOVjJ5UW1zLTg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17/07/2026 20:33</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
         </is>
       </c>
     </row>
@@ -1172,237 +1172,237 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 2 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Through the Seven Seas - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17/07/2026 12:08</t>
+          <t>18/07/2026 00:46</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPMmxUNlo2MFE2Rkxhdkh6U19sZjdFWV9DSGl5SThBYVRFWjdNY2RUS2RMVVFpbXJNaWU3SE9mT0VuRTJITl91Z2R0eF9KeVVRektwd2lBa1BUclEzaWtPbXkxVFZFLWg2MVJ4UUdoakZ3ampmc25aRkJqa2d4SjdYR1RPaTQ1LW5Cc012R1lKTm1aQ25Db3IxaEpjaWJWRm5lRjFvdHpUOXFhYS1oVlVnbzBCaHVXNzlSZ1FBNjJfQnp4SFVweHpJdWpqd2xZc0gwTTFrZHZDX05oRU5zWkhFME5XZEhSRU1PY3pqWDk1QkhuakhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWXJZMk5remlBSFU4WEY0TEtEcDhQNXVvRm9KemsyakoxYWpOU2pHdFdCUzg2SXdMc09MVkRVdlZ0VTV4TGY0anlPUG9KZmpla28wRlJDY3RqbVNvMEhQY0xyUG8zeWp2WjdZY19GNzFOV19MQjA5WUwxb1ZEbkhVQVc5LXEtQ0lNSk91N1hpczhVTDNBRDlPT25PczQwTTlvMzhfYWhwZVRxUWJEdWJNM0ctSGxaU2xSdHE3STdkdDZTcUk2dWJFdlJRMmFDUU5TbXZ5WDNLOEhqVzdEODhkX0hfYnpUQXlfUncwUllFbjlxUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
+          <t>Galeria de Mosaic Tiles in Barcelona Private Flat - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17/07/2026 10:55</t>
+          <t>18/07/2026 00:18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPY0xjMER6TGxTeHlsbTN1aVp1d2VSUnBtSVdsdDFYT1gxTmphd2xhc1lEeUtJdkdZdXZfcGZLeW9NYkZDd2xfdEd2M3UxbmtiTWxXRFFOTmdld0xnRnh1TWRjc3lXcEhpRkdsZDYyU3dZZXFyWWV2S2VDbDNIbGJVTFpZZmxGTHFRWWp3cXBIcUhBbnZCRl9hOFROM1JRck02NlJ4ZFNQSklGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cenário de fertilizantes muda ritmo de compras para a safrinha - Notícias Agrícolas</t>
+          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17/07/2026 10:27</t>
+          <t>17/07/2026 20:47</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPRkV6LWlUVmMwLV9sV1dVTloySVRoeXp2RWtnVWVXcVdVeXVQZEJyODNEMU1lYkUwMWR1Q0FEWm01T1A3Sno1QXAxdGNQclZEcjJTc0hoM1RKZ0ZTa2Q0enkyY3E1YmpYbm1SQ2FLMlUxT0JsZ3dLcUhlZ1ZmZXpzbkFGZkJQZUJBZ2FSWlBqTk8waG1YYTd4enE5ZWxjc0MzSU5xMkRTaGZ0V0xDR1N5bFBoWTNKWDczVUJ0VTI5QTF1WG0yT2RYSWRUd0fSAdIBQVVfeXFMTjdHSTBPMUtubG56aEdRb0ZIcnFEQzJSdGJPLXR6U0x1MjhFZ25BMEVqbmpJb2p2ZlJnaUxnR2ZDcTNyRE1adG1ZTG40b3VwaXd0ZnY5eEpUbGpBMlYtckJucUdaT01hXzJwSlBKcFAtcFo3WER4bU1ldTlFOFNkM19aOFlhQUFIUmFWcUxzM0NWbi1KV3JJX0lJR1NtckNDcVA3ZHVRekdKaFZOeDZlaUx6MG5EbzVvT0JRZ1hERFRKemNqZUltZDRubS10OWdoWWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17/07/2026 07:47</t>
+          <t>17/07/2026 20:33</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
+          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>17/07/2026 05:20</t>
+          <t>17/07/2026 10:55</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
+          <t>Cenário de fertilizantes muda ritmo de compras para a safrinha - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17/07/2026 03:58</t>
+          <t>17/07/2026 10:27</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPRkV6LWlUVmMwLV9sV1dVTloySVRoeXp2RWtnVWVXcVdVeXVQZEJyODNEMU1lYkUwMWR1Q0FEWm01T1A3Sno1QXAxdGNQclZEcjJTc0hoM1RKZ0ZTa2Q0enkyY3E1YmpYbm1SQ2FLMlUxT0JsZ3dLcUhlZ1ZmZXpzbkFGZkJQZUJBZ2FSWlBqTk8waG1YYTd4enE5ZWxjc0MzSU5xMkRTaGZ0V0xDR1N5bFBoWTNKWDczVUJ0VTI5QTF1WG0yT2RYSWRUd0fSAdIBQVVfeXFMTjdHSTBPMUtubG56aEdRb0ZIcnFEQzJSdGJPLXR6U0x1MjhFZ25BMEVqbmpJb2p2ZlJnaUxnR2ZDcTNyRE1adG1ZTG40b3VwaXd0ZnY5eEpUbGpBMlYtckJucUdaT01hXzJwSlBKcFAtcFo3WER4bU1ldTlFOFNkM19aOFlhQUFIUmFWcUxzM0NWbi1KV3JJX0lJR1NtckNDcVA3ZHVRekdKaFZOeDZlaUx6MG5EbzVvT0JRZ1hERFRKemNqZUltZDRubS10OWdoWWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
+          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17/07/2026 01:57</t>
+          <t>17/07/2026 07:47</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Niebla Swimming Pools - 3 - ArchDaily</t>
+          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>16/07/2026 22:44</t>
+          <t>17/07/2026 05:20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOR1FucXh3SjByRHcwWnpqc0dibDZJaGhTV2J3d3pNQTA1c3NReG1TWEpxWkpxZi1pamhTZ0JFRUxGOFpVV0VvNEktRUV2VTdaWFpXWWt4Zzk1YzA2WU5CaVF0bmtPVndvY051TU5yMnRTM01HZlI1bU9WelVTcGhESThaMkZYTHQxREtjUE9kMFpPOWJmbURJZDk4RlNINnE5NjdUcXAwUm9xS3BxM216M2RNRHV0Zk5XMnNiLWJpZktlUWRsU20yNWhUY2d3VndmVHBCdlZmanhlMVAteVpVZldtVG5ULTVPbmtiRVplcnY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Deep - 2 - ArchDaily</t>
+          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16/07/2026 22:38</t>
+          <t>17/07/2026 03:58</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYjl0VEdtOWlrM3BHdnBrUm5qaHFaZ0FON1dRT0F5U19Edm9KaG4waldtWnNBM1pMNVhBRGd0Znh0a3VCbzFLNTlCUzYwQktOU0xWV0I0bDQ3cHhKZEFrU0l6U1JYYlRKTUY2OHN4ZXBlUncyQlNabzB4Vm1EcGJaVXZGUk9ZLVZjdkR1OG1HbVhaVjlQWmdtaU9MOGJaUnZ0V0VGQjFVZDRRWWVHVEw2d2JVNWI5ZHZjMGhkalhkRV80and6Q0wyZzVvSmhaRGZvUXBxZGVzVWlCdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Galeria de Porcelain Mosaics – Olympic Series - 3 - ArchDaily</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16/07/2026 22:13</t>
+          <t>17/07/2026 01:57</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY1RfYzB5QWNIUm02bHM2NndzWnM3TnF3TjI2Y2ZabkFnYVpBeS1YUUpYNnNHZm52Q3BUNjlNaGp4eXZxbEloT2RVTDF4TUtnQ1NpRDBtUWQ5MmNrTkxQQ0FENlhFYks3d2otT1dwcnVMakhtSm5OUV9VY0ZwaVhoTGFLLVBZVzNiUmhSR3RhdTYzQWl4clJhYXJqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Galeria de Mosaic Tiles - Niebla Swimming Pools - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>16/07/2026 22:44</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxOR1FucXh3SjByRHcwWnpqc0dibDZJaGhTV2J3d3pNQTA1c3NReG1TWEpxWkpxZi1pamhTZ0JFRUxGOFpVV0VvNEktRUV2VTdaWFpXWWt4Zzk1YzA2WU5CaVF0bmtPVndvY051TU5yMnRTM01HZlI1bU9WelVTcGhESThaMkZYTHQxREtjUE9kMFpPOWJmbURJZDk4RlNINnE5NjdUcXAwUm9xS3BxM216M2RNRHV0Zk5XMnNiLWJpZktlUWRsU20yNWhUY2d3VndmVHBCdlZmanhlMVAteVpVZldtVG5ULTVPbmtiRVplcnY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1414,61 +1414,61 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Galeria de Porcelain Mosaics – Olympic Series - 4 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Deep - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>16/07/2026 18:02</t>
+          <t>16/07/2026 22:38</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNaUw5R1NLTUlpMWxBYmhvVWN5V1hUaVJjTVJXTHJwajg4UTN6bThCSXMybkhVTjZ5WGw0T2N1SUNpOUFybnFJaEN6Q1NKOF95R2JSNjdCTU1oVmlLOU96cjNFdGJfWEpBY0dJSXVPY1ZOSlZDLVo5c3U0SGdCYTExdlpmY0dOY3E4YmxHSDlLUVpsanJSY0FMN3JSaHFZclBmeTkxWlJFRHR5TExpU3R4d0dhcW1fcm9VV0FnSGFFYjRONkNfSkVOTll1VXBLa3VfcnRoMlRYR2pkOFFUTFljZFd0UEhGN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYjl0VEdtOWlrM3BHdnBrUm5qaHFaZ0FON1dRT0F5U19Edm9KaG4waldtWnNBM1pMNVhBRGd0Znh0a3VCbzFLNTlCUzYwQktOU0xWV0I0bDQ3cHhKZEFrU0l6U1JYYlRKTUY2OHN4ZXBlUncyQlNabzB4Vm1EcGJaVXZGUk9ZLVZjdkR1OG1HbVhaVjlQWmdtaU9MOGJaUnZ0V0VGQjFVZDRRWWVHVEw2d2JVNWI5ZHZjMGhkalhkRV80and6Q0wyZzVvSmhaRGZvUXBxZGVzVWlCdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
+          <t>Galeria de Porcelain Mosaics – Olympic Series - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16/07/2026 17:18</t>
+          <t>16/07/2026 22:13</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY1RfYzB5QWNIUm02bHM2NndzWnM3TnF3TjI2Y2ZabkFnYVpBeS1YUUpYNnNHZm52Q3BUNjlNaGp4eXZxbEloT2RVTDF4TUtnQ1NpRDBtUWQ5MmNrTkxQQ0FENlhFYks3d2otT1dwcnVMakhtSm5OUV9VY0ZwaVhoTGFLLVBZVzNiUmhSR3RhdTYzQWl4clJhYXJqQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1480,61 +1480,61 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
+          <t>Galeria de Porcelain Mosaics – Olympic Series - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 18:02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNaUw5R1NLTUlpMWxBYmhvVWN5V1hUaVJjTVJXTHJwajg4UTN6bThCSXMybkhVTjZ5WGw0T2N1SUNpOUFybnFJaEN6Q1NKOF95R2JSNjdCTU1oVmlLOU96cjNFdGJfWEpBY0dJSXVPY1ZOSlZDLVo5c3U0SGdCYTExdlpmY0dOY3E4YmxHSDlLUVpsanJSY0FMN3JSaHFZclBmeTkxWlJFRHR5TExpU3R4d0dhcW1fcm9VV0FnSGFFYjRONkNfSkVOTll1VXBLa3VfcnRoMlRYR2pkOFFUTFljZFd0UEhGN2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 2 - ArchDaily</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>16/07/2026 15:32</t>
+          <t>16/07/2026 17:18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQRVJGNHE3Wl9WZ1h0YjVDM3NSN2RkdllYVlZJTG9IaFJPSmdJcGpaemI5VjlhSHVuaklKd3hUMHJjQkZMTUl5a0dMSmtpa2gtdk9zckF2SWFyMGZHc0JhXzNTNnMzS2p0N2VuNk5oWTJkLUxxcmdmMmVQZ0pxVGh5eWVMaDhpWnZSMmF2MHc0Sk5RS2RBckFaNmdVYzN1SktScDZDVUZqem5FVlo3TmNDV3NmVjNUenJPY3otX1JkRWhvOHQ5aEd6NktKSXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>16/07/2026 15:09</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
@@ -1546,105 +1546,105 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 3 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>16/07/2026 14:55</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbWdlQXVxd2NvZFN4S0JDUjloZ3BieERuX0NjUlVOUkNPU2loOFFaM0pLd3YyQ0NnajRnM1BTRURWYVY0cFpwNnpjN1o1NTA0TVlGYnhvZ0E3S1AyRWd3aXA5MmUxbm1aS2FETVhSYnNmbUFrUThIYlA5QzhMbV9tT0pyc3F0RVF0RnBrLUdTMWQ4dG5OUlNwemVaRmZpbnFsSllVbWZZZnBnbldO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>16/07/2026 14:06</t>
+          <t>16/07/2026 15:32</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQRVJGNHE3Wl9WZ1h0YjVDM3NSN2RkdllYVlZJTG9IaFJPSmdJcGpaemI5VjlhSHVuaklKd3hUMHJjQkZMTUl5a0dMSmtpa2gtdk9zckF2SWFyMGZHc0JhXzNTNnMzS2p0N2VuNk5oWTJkLUxxcmdmMmVQZ0pxVGh5eWVMaDhpWnZSMmF2MHc0Sk5RS2RBckFaNmdVYzN1SktScDZDVUZqem5FVlo3TmNDV3NmVjNUenJPY3otX1JkRWhvOHQ5aEd6NktKSXQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
+          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>16/07/2026 14:01</t>
+          <t>16/07/2026 15:09</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f70678483fb8e8491f6ea9b03c&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
+          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>16/07/2026 13:33</t>
+          <t>16/07/2026 14:55</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQbWdlQXVxd2NvZFN4S0JDUjloZ3BieERuX0NjUlVOUkNPU2loOFFaM0pLd3YyQ0NnajRnM1BTRURWYVY0cFpwNnpjN1o1NTA0TVlGYnhvZ0E3S1AyRWd3aXA5MmUxbm1aS2FETVhSYnNmbUFrUThIYlA5QzhMbV9tT0pyc3F0RVF0RnBrLUdTMWQ4dG5OUlNwemVaRmZpbnFsSllVbWZZZnBnbldO?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>16/07/2026 13:21</t>
+          <t>16/07/2026 14:06</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1656,61 +1656,61 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
+          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>16/07/2026 11:16</t>
+          <t>16/07/2026 14:01</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab0486443d6be7df3bc10348dda&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>16/07/2026 10:25</t>
+          <t>16/07/2026 13:33</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeUJtUkdoeURpb1g4eEwxXzlWZnBoTF9CWXNYUTBaSU5NVmJXaWRXd2hIbTRFWG50N0stMVJHb28zeE42T2ppcjJXaDFSV19JeF9FVFFxX1RvVkdiY3pJV0ludVItcW1iQ05ZeDNYVVRuNVdsWEZPbTd1OFNvdldJT0dGV1RZOHJFNmVya3YzUEMxSFdidWU2X3JoSzdLYlFBVWphVkU1Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16/07/2026 09:14</t>
+          <t>16/07/2026 13:21</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1722,149 +1722,149 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
+          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16/07/2026 06:49</t>
+          <t>16/07/2026 11:16</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Black and White - 3 - ArchDaily</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16/07/2026 06:25</t>
+          <t>16/07/2026 10:25</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNc1hSUmhXOEZwM3luV29CMk5YblpGU2l6emlVSUNkVjVFSlEybEtnUlUtSUNCdWlLbjQ1bmNfOHFTNmpaZjJzZXg4UlJYVUJyQXdQamVkLWRDQ19yVHMzVjBDSTdFbE5KUUZCR1d0d2hTZkJ1WGdHU0xhOU51MEZ5dmdZU1dMTXlHSmtBMnpYMlc2OFNSTVF5LUc4TnE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOeUJtUkdoeURpb1g4eEwxXzlWZnBoTF9CWXNYUTBaSU5NVmJXaWRXd2hIbTRFWG50N0stMVJHb28zeE42T2ppcjJXaDFSV19JeF9FVFFxX1RvVkdiY3pJV0ludVItcW1iQ05ZeDNYVVRuNVdsWEZPbTd1OFNvdldJT0dGV1RZOHJFNmVya3YzUEMxSFdidWU2X3JoSzdLYlFBVWphVkU1Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Falha interrompe produção de fertilizantes na Índia - GlobalFert</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 09:14</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNV0hiVkZTcngtaVd0Ml92bEdzUGI5d085VmxhcUc4dGxQSE9UWlRiY3dkRmN3bVNsX1FPa3VrbllxRXc1NDczblBnRzd5ci1ob1E2RGpEUEZ3ZUpKR19DaDd1VkhpOU1ETG1DZWM5d29KSUpLWV9MVk9PODRaQ0VwVmI2TnhVQXBWa3h3bjI3NDNRNHNCSk9lVkJmaHA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
+          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>16/07/2026 02:55</t>
+          <t>16/07/2026 06:49</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Galeria de Natural Stone - 3 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Black and White - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>15/07/2026 20:26</t>
+          <t>16/07/2026 06:25</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOM3BvdVRNTzcxbU56MnhqZ0RVNzhBTGZ1azBibUxGUmttR2NGQ05SdEhKSjBpYVk4Sk5PN3Q1b0FkYUdqYTl1SWpUM05tRXNZUm45aV9pQmROYWM5M1JXYVgzb3NsbVcwYjg3ZkVSMTEyYjVUY0tqdkF0M0xkNlB6X3g0QXNINHZBMGcwV0E0cWVUOGxkXzVuOERfVDdrdGg1SFZkZDFtTEl6bHJPYmRIZGI4cldFVVlCUHJVVHhBVWJTYndYMkgzRkdmVmcxMVJleUQ0OWoySDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNc1hSUmhXOEZwM3luV29CMk5YblpGU2l6emlVSUNkVjVFSlEybEtnUlUtSUNCdWlLbjQ1bmNfOHFTNmpaZjJzZXg4UlJYVUJyQXdQamVkLWRDQ19yVHMzVjBDSTdFbE5KUUZCR1d0d2hTZkJ1WGdHU0xhOU51MEZ5dmdZU1dMTXlHSmtBMnpYMlc2OFNSTVF5LUc4TnE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15/07/2026 20:03</t>
+          <t>16/07/2026 02:55</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
+          <t>Galeria de Natural Stone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>15/07/2026 19:35</t>
+          <t>15/07/2026 20:26</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOM3BvdVRNTzcxbU56MnhqZ0RVNzhBTGZ1azBibUxGUmttR2NGQ05SdEhKSjBpYVk4Sk5PN3Q1b0FkYUdqYTl1SWpUM05tRXNZUm45aV9pQmROYWM5M1JXYVgzb3NsbVcwYjg3ZkVSMTEyYjVUY0tqdkF0M0xkNlB6X3g0QXNINHZBMGcwV0E0cWVUOGxkXzVuOERfVDdrdGg1SFZkZDFtTEl6bHJPYmRIZGI4cldFVVlCUHJVVHhBVWJTYndYMkgzRkdmVmcxMVJleUQ0OWoySDk?oc=5</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - redeutv.com.br</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>15/07/2026 18:30</t>
+          <t>15/07/2026 20:03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPb2s0Tlh5QzJKWnRDaWd2YS1sTHRsVk9Ccm0ydWd5ckVrRi1SMmw2alpOcklDNm1HWnpUT1lXQXVISFR1RTRhelJ3TDNpXzYzOWt0X1RzRl9yblBqa0ZMM3U3VzVRRjVCM2E4NG1tOWxkVF9GWFFYblFURmNnbHNiOXJPVUFEcFBod09EbUdDdlN4OUIwT0pSQksyT2E1ekx0bXpadWpyTUFORHp0LTk5cHBodWhSdzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Starlight - 2 - ArchDaily</t>
+          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>15/07/2026 17:37</t>
+          <t>15/07/2026 19:35</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdmk4b3VieVVYVFpjeUhPdXBJRndnZmdnX1EtWmJhNGFZcVZUVzUtelhiNmxxTXFieGxFd295c2w1WEk2UHJrc19iVlB4dkRBUTFmWkVZX1RHcFczRlRzVEduTy03WTRNNkZEYVk5Y2VVMExaR0JaeEl2MlhudGJrcDdHT2d6blJ4bDBfdWMzeWFZbVRi?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1920,39 +1920,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - redeutv.com.br</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>15/07/2026 16:45</t>
+          <t>15/07/2026 18:30</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPb2s0Tlh5QzJKWnRDaWd2YS1sTHRsVk9Ccm0ydWd5ckVrRi1SMmw2alpOcklDNm1HWnpUT1lXQXVISFR1RTRhelJ3TDNpXzYzOWt0X1RzRl9yblBqa0ZMM3U3VzVRRjVCM2E4NG1tOWxkVF9GWFFYblFURmNnbHNiOXJPVUFEcFBod09EbUdDdlN4OUIwT0pSQksyT2E1ekx0bXpadWpyTUFORHp0LTk5cHBodWhSdzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>Galeria de Mosaic Tiles - Starlight - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>15/07/2026 16:02</t>
+          <t>15/07/2026 17:37</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPdmk4b3VieVVYVFpjeUhPdXBJRndnZmdnX1EtWmJhNGFZcVZUVzUtelhiNmxxTXFieGxFd295c2w1WEk2UHJrc19iVlB4dkRBUTFmWkVZX1RHcFczRlRzVEduTy03WTRNNkZEYVk5Y2VVMExaR0JaeEl2MlhudGJrcDdHT2d6blJ4bDBfdWMzeWFZbVRi?oc=5</t>
         </is>
       </c>
     </row>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
+          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>15/07/2026 15:41</t>
+          <t>15/07/2026 16:45</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>15/07/2026 15:16</t>
+          <t>15/07/2026 16:02</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
@@ -2008,39 +2008,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir ‘cheiro de enxofre’ do futuro dela - Jornal de Brasília</t>
+          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>15/07/2026 13:40</t>
+          <t>15/07/2026 15:41</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOR3F4ZmpKWHBhekMzRTJkVnhwUjNHdVJwSWVlbHVHMzJiTDRwbjN4Sk80SXprQzI0enRZUW1kQ2s2RVJ1XzRrNHZiUHNUZThaSmU0THRYa2pzbzI5MGJ0dVZNZC1CcF9kMHNxY3c4ck1SanczMFpmMERwZE9KamF1czBZb3doWGNwaGVETkx6R3NhRlBxQ0V6NGM2WmVaaVpSX2czVzFPU0ZFaDJNV2p1Sm5YTHpIeWMtWV9uZUlrRGFqZ3E1VGkwY3hGdEVMRVJJaGpseXV5M0tQMlJpM2hnTDNYZmVmSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
+          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>15/07/2026 13:10</t>
+          <t>15/07/2026 15:16</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2052,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir ‘cheiro de enxofre’ do futuro dela - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>15/07/2026 12:35</t>
+          <t>15/07/2026 13:40</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOR3F4ZmpKWHBhekMzRTJkVnhwUjNHdVJwSWVlbHVHMzJiTDRwbjN4Sk80SXprQzI0enRZUW1kQ2s2RVJ1XzRrNHZiUHNUZThaSmU0THRYa2pzbzI5MGJ0dVZNZC1CcF9kMHNxY3c4ck1SanczMFpmMERwZE9KamF1czBZb3doWGNwaGVETkx6R3NhRlBxQ0V6NGM2WmVaaVpSX2czVzFPU0ZFaDJNV2p1Sm5YTHpIeWMtWV9uZUlrRGFqZ3E1VGkwY3hGdEVMRVJJaGpseXV5M0tQMlJpM2hnTDNYZmVmSFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -2074,17 +2074,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15/07/2026 11:51</t>
+          <t>15/07/2026 13:10</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2096,39 +2096,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
+          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>15/07/2026 11:09</t>
+          <t>15/07/2026 12:35</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Guerra no Irão: Empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
+          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>15/07/2026 09:49</t>
+          <t>15/07/2026 11:51</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxQMTVEaUdSWE41ZlVJWThHNVNBRlVFbTd4LWpjc3J1Z3Z2QWFxa1NBVS1VMk1YYU5OWGxlZEJmR0gwb01ieXVmN1pjWmFwOGJ5VlR5N0ZiTWlSV0l6dDdRQ0h6dFFGVmkyRGxUa0tHM1d3SWd1Y3hxUlNsWExKOWxOelNzaDZZdTh3bXg0XzVLWjlLMzJieF9qYmFzRWpFRk9pR1Jzc2tnM2ZxcUhUUmxOSVlVUjFmSFhwTTNnMllCcE9aWEtxNkppYVpDWFhoWFVLUWc3Qm1uWjNab05fRnE5djE0cmw5Z243NlhCaDlMOXVyZUU4YjhjQW5zdWlIbFhhbWhzVHZpR1lBY2ZvMFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
+          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>15/07/2026 08:00</t>
+          <t>15/07/2026 11:09</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2162,149 +2162,149 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
+          <t>Guerra no Irão: Empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>14/07/2026 23:07</t>
+          <t>15/07/2026 09:49</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxQMTVEaUdSWE41ZlVJWThHNVNBRlVFbTd4LWpjc3J1Z3Z2QWFxa1NBVS1VMk1YYU5OWGxlZEJmR0gwb01ieXVmN1pjWmFwOGJ5VlR5N0ZiTWlSV0l6dDdRQ0h6dFFGVmkyRGxUa0tHM1d3SWd1Y3hxUlNsWExKOWxOelNzaDZZdTh3bXg0XzVLWjlLMzJieF9qYmFzRWpFRk9pR1Jzc2tnM2ZxcUhUUmxOSVlVUjFmSFhwTTNnMllCcE9aWEtxNkppYVpDWFhoWFVLUWc3Qm1uWjNab05fRnE5djE0cmw5Z243NlhCaDlMOXVyZUU4YjhjQW5zdWlIbFhhbWhzVHZpR1lBY2ZvMFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily en Español</t>
+          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14/07/2026 22:11</t>
+          <t>15/07/2026 08:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
+          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>14/07/2026 21:19</t>
+          <t>14/07/2026 23:07</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
+          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>14/07/2026 21:03</t>
+          <t>14/07/2026 21:19</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>14/07/2026 19:16</t>
+          <t>14/07/2026 21:03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>14/07/2026 17:57</t>
+          <t>14/07/2026 19:16</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fertilizante em alerta - Olhar Direto</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>14/07/2026 15:27</t>
+          <t>14/07/2026 17:57</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab1f71e48cda3bbf137739e5fd4&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - O CORREIO NEWS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>13/07/2026 07:14</t>
+          <t>13/07/2026 07:29</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOSGE2ZEdaY3pESWY1LW5oWnVIRW1HSWM1bUJfZ1Z3RVI5RDJvdFJlOGpqZkFaYnAxM05iZHh5T05UeTl1dWZKZHZyUHVRd0NFUTR0d3hkbHF1dFJWZUJocUxVMmQyVnhrclQyQ1lGTXNIV2FmOG9EWnhac01uZmZKOU5DWGxIRnJTaUxaVFA5WklOeHVaakpZZWZsZVhXcWctX0dhdDlOU2VIY2w0MXp6X2NYZWJQUmtyR0UxZ2lVZzFLd0lFQU1GR0ZuQUoySlF3U0ZvOEpiZlA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2910,17 +2910,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>Mosaic prorroga paralisação temporária da unidade de Catalão por escassez global de enxofre - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>13/07/2026 04:00</t>
+          <t>13/07/2026 07:14</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWV4dkpSb09jVG43Rk5yY3oybVJnNXowZjFORV9XWUdMMVl1X3ZvYkVkYnk5d3dtNVIxb05IcC1aeXQzWFJjYVFCbUdjdlFHZHlWS2Naa0ttY0dNaVJodGtNNGRaaWVwYUFja3ctQlluZTZVUVdYNWF6V1MwVE00MlVOOGhDNkJvSFU1VFlqd2wwa3hnczdVNTFyVmpxWTFnTnl3RlU1QjRyUHdBYWI4Z0UxQ09QdHBkQUVrZXExc18tUkptWHNsekp1YnI?oc=5</t>
         </is>
       </c>
     </row>
@@ -2932,17 +2932,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>12/07/2026 11:31</t>
+          <t>13/07/2026 04:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
@@ -2954,39 +2954,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
+          <t>Mosaic prorroga paralisação em Catalão após crise global no fornecimento de enxofre - Diário da Manhã</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>12/07/2026 09:51</t>
+          <t>12/07/2026 11:31</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOWs2WThKNnh3N0pGT0xNMWRoc0xuWS1aSW9ZMFlUWVJmSllnLVZieEpiMVhwSTkwcWVoeUJWSGo4MWVqX09QU0Z2YXlOSXpuZW9saTZJTjBxbU1fOVRRWl9SVFV5eEM4bXRzX2Q2X0trV1RnQzZXb2M2MXVNMXFBM1RkcmJjalJmSW1mOEl0ZGlESHJnUXpuYlJPdkQ0TDNDeEE2QzVMYWx2RHZONS1ldXhoeEdnUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Inteligência artificial decifra as regras de um jogo de tabuleiro romano perdido, encontrado em uma pedra de 20 centímetros na Holanda</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil e unidade de Catalão terá paralisação temporária - Mais Goiás</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>12/07/2026 09:44</t>
+          <t>12/07/2026 09:51</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f70678483fb8e8491f6ea9b03c&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM3VPUnViV3c5azFIVjI2U2s1QnJuRm90bXJreE0yS2hJVlJOMlY2bm5GNlBBbHIxc0xSZEU1RzE4d1E5bTYzR3NVMy1mNUtIeklma1RJNWFXcWxBTUYzT3VEUndQb0JidTh3S0R6T01XQ3lOQkptQVVoZ2VxWF9fSDRwTHFoa1pLNVFkTE1paU1UTDBIbnhYcEprNndQVHJVekRHd2ZlanRYM0Zra09LR3VSZmVNdzhPMUFqNWFFRFBjNkFMSzZObXdzQnFYa2V6?oc=5</t>
         </is>
       </c>
     </row>
@@ -2998,83 +2998,83 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
+          <t>Inteligência artificial decifra as regras de um jogo de tabuleiro romano perdido, encontrado em uma pedra de 20 centímetros na Holanda</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12/07/2026 07:11</t>
+          <t>12/07/2026 09:44</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab0486443d6be7df3bc10348dda&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 10 - ArchDaily</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12/07/2026 06:03</t>
+          <t>12/07/2026 07:11</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNaWdNVDVyUi1tZURyb1ZtdUlTdnRGNlNvbjJNY1lUa0RwRHVKZ1pyOTEzZ2N2d0xtUUQwSmpOS0RjbmJhUWE2WnYtU1lkZWpwejM3TFU3LWJwQmx2UVlNU1NLQ1RqTkNjLUgxZmN2cEJHVFNaSGFsTzEyLXM2ZXl6ZlZwNnJzWUF2NHlnNzZFZVFpSWEta25zUk5xcXkxYjM3cUw1VUJlUzRQTXNlTWdueVRKS1lmOUtLLWVBZVN1aDhwZnEtX05CUTJrMUN6bFVheGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 46 - ArchDaily</t>
+          <t>Mosaic anuncia paralisação temporária das atividades em Goiás - O Popular</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12/07/2026 04:41</t>
+          <t>12/07/2026 06:03</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNbnJNcWZjMnh4QVQ0clU5aGdHU3ZqRmNGdW9nT3NhMEQtSTdsRUYyUnJBci1KMklLbTFKU0FZUUVKN2JyN3ZYU2d6YnZTaVRUNTlCNlhKSHppdjNHcm95bWNGRkotbkVvNkNGZS0yZjFaeVU1VndTWWppaV9GTWxKRTVBeFgyMnBkak4wTnNKbFV2SVQ4RDZJcktmcGRaYjAwdlNnWUNpdGZYc1BRcTdVWjFXU3lQVmtOSElpWFNNdkNKMEpLTEVGYWhvR1FGSUJid2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd1hMbnIzRXEzWC13ZTRoRXcxbDhCeUhEbkRYY1ZObjhPczh6RlpSZVEwck9FelpCT0pzcGhST2xDMHNTV1dRdDIyYWQ0T00wRXFnaHd5VDc2SDJqbmlvTzg0Rk95R3VaUktfaUp4VFZBT2FWaXJEbFBoMEloOElESjVtUkNRQnJ6a3A4SGhTZTVWQXdpb3RpZUt0X2EyVmFGSGs2cXBoVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 46 - ArchDaily</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>10/07/2026 20:16</t>
+          <t>12/07/2026 04:41</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNbnJNcWZjMnh4QVQ0clU5aGdHU3ZqRmNGdW9nT3NhMEQtSTdsRUYyUnJBci1KMklLbTFKU0FZUUVKN2JyN3ZYU2d6YnZTaVRUNTlCNlhKSHppdjNHcm95bWNGRkotbkVvNkNGZS0yZjFaeVU1VndTWWppaV9GTWxKRTVBeFgyMnBkak4wTnNKbFV2SVQ4RDZJcktmcGRaYjAwdlNnWUNpdGZYc1BRcTdVWjFXU3lQVmtOSElpWFNNdkNKMEpLTEVGYWhvR1FGSUJid2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -3086,39 +3086,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - Portal do Triângulo</t>
+          <t>Anderson Adauto articula ação com sindicatos e promete levar crise da Mosaic ao governo federal - Folha de Uberaba</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>10/07/2026 19:30</t>
+          <t>10/07/2026 20:16</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNRlJham9kdHJzUmhUMktiUXFDbmRqbWRYMTVEMGh6c3c0M0ZQVElEYlNJMHdoekRNTzhGeHNRai1MYkp3XzU0aFRiUEpGMUZtSC0xcXVkcGZiOFlWQ0VMZWx6ZFNxZnc2Zm9xLS1fZ2k4V0Jqd25XZGppODlmbkRlTkNva0JXVE5FeWNaSWt1MXdjcGJlV20zUThPSk15TDZoanZaYjlpakNMcEU5WGcwUjVhbUYtYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQbjRwcEFiRTF6ZlBDOE9FYmt1ZnJQVjZXN3FmSTJwaENRUDNYWm5rR25PY0dWb1lUdGhxeENUNFMzdS1ubnI4SEZUa3NQbVo0d0t1RVJoT2tuRUM0MFpCMy1yMnc5LVcwZHd2YmgzVDFZc0V3YUZ3ZmhkWnE2VXJNZE5FV3B2eW41ZGhHMDNPS25aNDhxeTloZ1BwU0VQclJfVEs3M3U1a2FYalBqMmcwMFg1MUE2aVVCaXhYNGRLRHhGUXZjYXNF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - Portal do Triângulo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>10/07/2026 12:37</t>
+          <t>10/07/2026 19:30</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNRlJham9kdHJzUmhUMktiUXFDbmRqbWRYMTVEMGh6c3c0M0ZQVElEYlNJMHdoekRNTzhGeHNRai1MYkp3XzU0aFRiUEpGMUZtSC0xcXVkcGZiOFlWQ0VMZWx6ZFNxZnc2Zm9xLS1fZ2k4V0Jqd25XZGppODlmbkRlTkNva0JXVE5FeWNaSWt1MXdjcGJlV20zUThPSk15TDZoanZaYjlpakNMcEU5WGcwUjVhbUYtYTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3360,19 +3360,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab1f71e48cda3bbf137739e5fd4&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mosaic reduz produção de fertilizantes no Brasil por escassez global de enxofre - Canal Rural</t>
+          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,19 +3426,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQSWJRLTNNNlZ6Y2hKcDlTblhmZFY5WUZhWUlYTUlsY2l3TXpMTW80bjRYeE9GdTNCYm5UVzVvMzZZVnR6TkxlbTQ2YjAyc1YzcFNqbHF5Qlh3MkhSdVgyRmROODdoR1ZIbjEySkdPZ3N3am5uMUFRTDQ4NDVTVEZYbWJfQldRMmpFaDBTLXRGU244czdfMEk2Z3JGbUNrMmNCMDV0WWZtb0tKN0xGM0dCVXB4d0I4M2FFZlZZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
+          <t>Após Tapira, Mosaic vai paralisar produção em Uberaba devido à crise global do enxofre - Diário do Comércio</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5oZVBCaHBGRUI5T2wxMWZRNHVOaTczM0toNkR6ZEtfMUI4NzVhTjFSOHZ2VFBwN0pld2hGSjc1VFo0WHlSbDFUUkNsOVFreXZNMzBTWmlaemthSGVienVwLXJYVGRMRFZpbTFtY3hiRU9OVGQ2bUdGQU9PaW0?oc=5</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87febec14f1e91ab9d65ce9907a5&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab8c9b54e53abc5bf566e4fea64&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3624,19 +3624,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Alta do enxofre provoca crise na produção de fertilizantes em Minas Gerais - G1</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQYnY2QmNpaXc4aHRDMDFLUmxTNzhRME9pNWhac1psdWtNMXMwSHJsN3oxeUJqNXZtOHVNWUNaQnNjOUJaLWRhbF91M05Sa3VIM3dsTjM2X2VLSS03ZTlPWFF4T2xLMUdzTlZLdk9tblk1WHRZUWtGT3BmUktDODYzMU1VUTEtbVc3N0VTelc4ZUROZDBkX2xZeFlma01wMjV3WHBISVdRQ0lwYmFseFA5d1ZnNXdFMVpRUk9zeHJpbEUzQ1Y0MUdpbXdiTnlSZ3o2ekJfbnZOYlNJU29nU2FaclhFR1ZqUmFx0gH3AUFVX3lxTE1sQjBVb2UzRGxTdGVBTXd6Y0lwX0pBUmYtOXIxYmU3b2EtLUtLYklfS3FHcHp3VklkU0xtdjlwMHAxYzJtNmcwNHkzOUd6TFBZZVkxa1VWVmJBRFZKLXFSLUpxQnc5al8ySjRJQkNFUnpWRXlmbTctMlp4SXd4OUJSai00ZGxocEd6dUVZbE8zZ0JXaDJ2SEllampRdER2aF9IRlBoMDZ4SHZ4UXhqT1RVYVV5ekFOSTVyUkgxQ0RJNzQ2N2ZfQThQR182WUVGQ2ZVNHBKOUtuVktNNG5LTVBnX2tUbGNHNzhOQkpuMEhjR2RBTHJYVkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Martin Marietta anuncia aquisição da Lhoist North America por US$ 13,5 bilhões - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNYXg3YkM0VFFac3BVN0QwMmZqYm9rQW9XM1ppUzRJTl85Y3FkMEhHSFY1Q0NON2pxTE9uTUNob0N1bkw5bFA5Y002X1VVTzdLT1JmdDFGUk16cDBJaEc1eFdLdlZwNWYtZXFxVnVjUnA5QlhWaGhFZmJUalBLQXpJZFF2TmpmVjZfZFM4THVXQndEUUlZYnI4X3FLY1VoQ2tNY1NyNFVZVkpaSmdxanJwQTVxcGJCNmxtOTBOZklvY3JlbzQtM2NMX0NRZmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,19 +4042,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,19 +4064,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,19 +4108,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4142,29 +4142,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>25/06/2026 04:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Na mesa, subsídio para a indústria de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQVldCXzBjWUpNeVRUS2VwQktZY0hiUWRtUk9vTExVZHQ3R3F3ZURhWnFtNXdtc0dpelBoYjAwaGEtSlc2UnZJbnpublIxa1l0ZjAzdXdVVUFJYXVSYm5Ec2JZa2RjQm95cmlycFdBWGFNUWhEcHBZb0JLbDBaZGMwVmdraDlOQVFMWnppalExTTFmQUJudnlRSndDaHY?oc=5</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,19 +4218,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4262,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4394,19 +4394,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,19 +4416,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4482,19 +4482,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>O recuo estratégico da Mosaic no Brasil - VEJA</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNcWNOZnE5TE9kN3JvVzA4eThSNEV3NFVQanBMcm1WdVd5YUhoa2N1UFlTMTNvUXQtNDhoX05LeGlGRlBLNzBfeGI1VnNJV3M0NklZLTBhNXJEY0FwV0YzMjg3Vm5iQzJ5OFV0UkRqbThiTjhmQ1ExX2V3MnFJbEM2c1RZUkd2QS13YWxwS0w4Z2stNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4944,19 +4944,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,19 +4966,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,19 +5010,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
@@ -5088,29 +5088,29 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,41 +5120,41 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,19 +5230,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Enxofre deixa de ser subestimado e se torna pilar estratégico na fruticultura - G1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQd0lEN0lwUl81REtIblJHeWQ3bHVXWFZ4RFN1UGVWa3ZEOElINDFVeVBEZElIN0d0eGc2b3RxeTZrdThaMThmWHl6aFlkUW8wVTBDYUE4dDRSSzYwc253NWVmVWtiamlCeEt5SmVqa1NyVjB1eGVCdzQ3elB5N3B6ZjJLVmpnUEpVcjVIUkxMOFdQUzVHc0xOdlVaeGJTVW5peE4weV94WlJTbld4NzQxZHF0R3lYeU4tYi1kMzQzMTlzVmtLUDdPRGRZQ2JLSXFMbmdHbjZ0dTJEd2ljT1lyZmJHZGFXbndIVWJ6UDNXQlFNejFKSlJXaUlkX0FrM29vMVlEWjJNZXd4bGPSAZoCQVVfeXFMT2NaQnpsUDF2RExvbHRMZHM3dWhJQVFPX2p3a3FUejB0djlRaUFMM0duYjJmRjJKWWFnRmNScXJMNnh3VUd4QXNHbzh3VlM0dlVDSVZGc1l3eUNKZmpva0IwQzFORWVjM0NZT01RSHBxYUlOTl8xU1hlMHFPVkRvczhEbm5xTDVoVjFNaDNiRUdodmdEQmxBU0xNTTRtVVFuenVoZjFYODBEclU2cFR3NkxBR3dkaTEzb3BlbE9oYUhIRmJNSm9RVlFBLTV0aUhOTHMzalloZXRCX3NLbVVjOU55WGY1N0hVVXI3UUNsVU1DbjFnV2p5V0VPOXZHaG1td3V3TGxGTmw2R1VwQ0Y5UXkwTkpsUGI0cUh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Enxofre deixa de ser subestimado e se torna pilar estratégico na fruticultura - G1</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQd0lEN0lwUl81REtIblJHeWQ3bHVXWFZ4RFN1UGVWa3ZEOElINDFVeVBEZElIN0d0eGc2b3RxeTZrdThaMThmWHl6aFlkUW8wVTBDYUE4dDRSSzYwc253NWVmVWtiamlCeEt5SmVqa1NyVjB1eGVCdzQ3elB5N3B6ZjJLVmpnUEpVcjVIUkxMOFdQUzVHc0xOdlVaeGJTVW5peE4weV94WlJTbld4NzQxZHF0R3lYeU4tYi1kMzQzMTlzVmtLUDdPRGRZQ2JLSXFMbmdHbjZ0dTJEd2ljT1lyZmJHZGFXbndIVWJ6UDNXQlFNejFKSlJXaUlkX0FrM29vMVlEWjJNZXd4bGPSAZoCQVVfeXFMT2NaQnpsUDF2RExvbHRMZHM3dWhJQVFPX2p3a3FUejB0djlRaUFMM0duYjJmRjJKWWFnRmNScXJMNnh3VUd4QXNHbzh3VlM0dlVDSVZGc1l3eUNKZmpva0IwQzFORWVjM0NZT01RSHBxYUlOTl8xU1hlMHFPVkRvczhEbm5xTDVoVjFNaDNiRUdodmdEQmxBU0xNTTRtVVFuenVoZjFYODBEclU2cFR3NkxBR3dkaTEzb3BlbE9oYUhIRmJNSm9RVlFBLTV0aUhOTHMzalloZXRCX3NLbVVjOU55WGY1N0hVVXI3UUNsVU1DbjFnV2p5V0VPOXZHaG1td3V3TGxGTmw2R1VwQ0Y5UXkwTkpsUGI0cUh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,63 +5318,63 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5406,19 +5406,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,29 +5582,29 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,29 +5648,29 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -5682,29 +5682,29 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,19 +5736,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5758,19 +5758,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,19 +5824,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,63 +5846,63 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5978,41 +5978,41 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6022,41 +6022,41 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,19 +6088,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6110,19 +6110,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6161,34 +6161,34 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,19 +6198,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,29 +6220,29 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 14:18</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo no 1º trimestre e reduz produção diante da alta dos custos de matérias-primas - GlobalFert</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6528,63 +6528,63 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxPUFFYa0l4STNuY0phdjkxVi10MTN0WnVnTGp5bVVrWDRKajFzZm9nRU84MEtLNXdYc3dQZHE2LTNfV2poUGZHZ0xuWGlaS0pRUmRfTlBkeERWMmxYZ3FNd3VYZWQ3ZUdHc3A4eExHeU5ONTRJREpud3ZnZ0puMW81TXJlbFBmdGpWQnljWU5nMURSNDZ2T3psV2tYdjFrNjl4Y3Mya19id3NKUlU2ZEdJcFBQNE02OXRseU9HMmdmaVlBdFdwa3MyaklWX1JVRHBkbERaTWllZXhEZ2NHaFNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,19 +6638,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,19 +6682,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6704,51 +6704,51 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6770,51 +6770,51 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,19 +6836,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>05/05/2026 04:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6892,29 +6892,29 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>05/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,19 +6990,19 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Mineração vira aposta bilionária no Equador: China fecha acordo de US$ 1,7 bilhão para explorar uma das maiores jazidas de ouro do país, promete US$ 4,39 bilhões ao Estado e amplia sua força na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNYWlRUWx5RGM2b3h1UEJTdzNRcmRXVzRRQjBWcFY5cDRiVjhwMUIyeE9tdGh5LXUxLU5QcUxxNDBfQkVYa3BWVUV0enZxYlh5cDVISlNNY1ZRVXd6LXY0bFgwQ2diUUp6YmtWb3gtSTZQR0hfUmE5Y2dpWXk4RW03MVVfODFZNmt0Y2hORTQ3TEZrWmR5TXdfWlNuLU9HSTItUGQwb1R5R25zWi04ZzdsU3VWcjJUVnJzaFdzT2pQQkp4RDBSR0NOX3hmXzBmSGdxQk5hcU1aM2ZLMkJkRmpZRjI1enBHN25HVWw1TFVpMUxfTTY3bF9hdUxQZHZzTFpPaDloMzh0cmJfZUUxeWJHSUNxdXFkcnFVQW1Bb2xQYnhYZ1J6U2xJNWtRbkZHbS1D?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,17 +7046,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,17 +7068,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7166,19 +7166,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Para reduzir dependência externa, Petrobras volta a produzir ureia no PR - Monitor Mercantil</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNaFN6dXlpRHRuQWNMd3NybU45VF9fdkNMQnpOTmd2bGhMZ1hYem9qMmlnNTFNNWM4X0RYak56XzNpaW01NFJtalZ2TFp6STNGanpKUEhLREFkejZackdaRUN6MmRUS2FteUxpSmFpTlpfTG5oV1JncDBqZjFCaFpCRlIxeWVaR1J1blJrbkdZT1cwUVd5ZW9nRlozVlRObWR0Q1ZUMERRQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,19 +7254,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,85 +7276,85 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 30 de Abril de 2026 - RRMAIS</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOUXhYaUtDQ3pyNUxlZFV3ZjlIYVFHOTNhV21VN3RPdFNGTUYtSWpURXVnZjlhWHl1cDdfN3phMmNDcmQxejFrVkdqdG96Ymc2YTFwLXlzaUFsZXFKaG5GZ2Z2c3pCMnBuZk14RjVXclZlRmhjbVdfMUFXUEFOVVBNVl81NzdCdlNJQXhPbE01eTJBX1hPRm12dC0ybURMV3YtbG1aUldwSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7364,19 +7364,19 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,51 +7430,51 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7547,44 +7547,44 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7596,61 +7596,61 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7679,34 +7679,34 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,29 +7716,29 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7772,29 +7772,29 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - O Fluminense</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,19 +7826,19 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 inicia em abril com sete clubes da Região Centro-Norte - O Fluminense</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNTFV2aE9QamdoTlhzd051c1VfLWpKQTdQcnNoM250c0dZd0VUd2NTMG5MWW1laWY3N2hEVkp4cUNNelJDam1WWFZOMHVrNUdONzVFVlZrNS1CaHBSVmNwV1Q2QmxyM0tqVnF3MmhDLTA0ajJXeGUyRUN0WlQ1dU9CeVZPTHl5WkdHN2xSVDBfdXo5Z2dFaUN5UnY4RFN4clpkU2taZ2hDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,29 +7970,29 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8002,29 +8002,29 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8046,51 +8046,51 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
@@ -8119,22 +8119,22 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8163,100 +8163,100 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab1f71e48cda3bbf137739e5fd4&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8295,44 +8295,44 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZGVwSXBCbHh2T2tRbE1KQk9NRFZIQ1JuaUl3S2lKcVZ2bXlhb3dnOHZHRGp4dVgxRU9ObWxMM0hoTFZXQkh4RlJHVktzUUppdGFINFVBeWNRSVVHR1o1eHVpQU1HZTROWmM5REhaa25xYS0wc0p3ckVsZkNmRGp5Ml9Cd055NUxHWkE5OUEyMlM0WmRuT0o5RWNob0NEdmFFUW5qejJpR00ycTdUQjFMWXVTZFpwaWliTTBJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>21/03/2026 04:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZGVwSXBCbHh2T2tRbE1KQk9NRFZIQ1JuaUl3S2lKcVZ2bXlhb3dnOHZHRGp4dVgxRU9ObWxMM0hoTFZXQkh4RlJHVktzUUppdGFINFVBeWNRSVVHR1o1eHVpQU1HZTROWmM5REhaa25xYS0wc0p3ckVsZkNmRGp5Ml9Cd055NUxHWkE5OUEyMlM0WmRuT0o5RWNob0NEdmFFUW5qejJpR00ycTdUQjFMWXVTZFpwaWliTTBJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8344,51 +8344,51 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - CircuitoMT</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>21/03/2026 04:00</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNVkFwWkxpMVFhdFh2WDZORExyazZ6WWZucVBZS3pzVlhNbHh6ajF0RXpYRG84cFZWWDBwMmY4LWdaNUdfM29sQW1wVE43QXNSbjlpdmlET1g4M0RCRkI2R2loc2xpaFgyUTl6U2FFSUhNUlJTVkRvV3U3TlZtM0RQX05MaHRRcE42ay1kOG9aUHdISHIzMWJ6SXpjdldUZEk1ck8yQmhhTWN3djlXUDkyYWZZTGo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Alta da ureia pressiona mercado e pode impulsionar uso de alternativas em 2026 - Feed&amp;Food</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOZWl0bUdaQVRHdjR0MVZmM1kwREFfQjl4bl9pM3RETHFoc2QwUThjcWdFUmxzQnNSZ1Q1VjM3dXE0NXV6dEE0eURjNlZVTXVLZXpZVDdERkZWMVBjcjJjd0lrQWowSFptbVBpVGx2c1V2WDdweUJYQ0l6RVlHdHZUbXZKQkdKMDVxVkVYekV3dnhzUk5QeVd6WHZiM2pLU244eGk4SjNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8420,41 +8420,41 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,19 +8464,19 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8486,19 +8486,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8520,39 +8520,39 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8564,17 +8564,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Com a ureia mais cara, produtores devem priorizar sulfato de amônio em 2026, diz consultoria - Globo Rural</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQT2xzWXcxV2x2ZVhmUkRkaC1UcnhNc2ZPVnRGZEhNTS05SFNxXy1VX2lybU9xckFIWlQ5VHVqMDhmVHNadTQ1ZGhzOS1GdEdKVkFvclhwSUxKS1VzUkM1dXRKSGp0cGdBb1I4UEpZWF9MOWFKYkhoR3Mzbjc0MVlqLWFVWVZjV1F4WHk5aVFLdXB3aGJMVjZNb293QVJ6dFFwTXFmYnl0N3YwcWN3WUxDRXdJNV93WExvb2ZSem1pYWJxb2xpWHhUZEprVGZPMkJSMG9OVWIxeWF2NXgxZzFtekl1Z9IB8gFBVV95cUxOMTBUbUNYVHdQcVhtUnpmWnJLVDY2UlZmUWNvY2VMT0FaMllxSVgyMC12SjEtYjRUM1hUTk5UNE8xRUZEcFo4VmpjTDJ1VFZld2tDdWlyUklickYwRGtQQWY0V3pRMzVqMmdjMFJWUEZiLTBmRnc0Q21qS0taVWJRUG0tT1pVTU5YTGdZTGM0NmwyV3hVMEtNQ2FGRnBQVExRbmdXTUlPN2VZVno5UUxHWmE0Nk1SS0hsS2xrNUU5N0p2QWxiS2E1Z0NYeW9LcEFodEhXNXR1d19QQWpFVDFJa2l4U3N4ZUZRMWthWmd5VWVSUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8603,44 +8603,44 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar sulfato de amônio em 2026 - Notícias Agrícolas</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQNzYxMi1VVEdnMTlnT29ZUjhKMmN2a0RZMVR4X0o5Yk1QZkdLYU4wZVQ0RGlqYm1hUVE0UnJtcUl6MXdpYXcyYzdGdzZRaS1aMVI4UnNTeHRqa1lnSzl0eFNLWmxrSUZrRUpJU2hpWm1NSnhIRVBYZjh3NEc3UVJIT0stY2ltMWxITUZaODVtSllTd3BqYUtYMHA4eE9OSnFsZTU5MDFOQnhsa2xZRU5HY3FmUU9ILW5peko5dklXOGN1QzlPYUlJRnhPaVljTU4yQzdrMll3ZGpPVWlrUGfSAeMBQVVfeXFMTThXa1RleEtxQzR1a25yZThEUFAtajRDZEtFbFpnOFk2TWYxcUJ4UEtEYzVYdmF2YlFEZG9YTlpKam5yeUVJLWczZlRWR1pseS1CMzRENXcyUVhkM212UEhaMUhUTHJWTkZ4WkFwQWktck1ob1BwejdieXZPdjNFNzUwM1ZGUG9wamktbHhFM2FlQUhnWW92YmtQZ2IxOUoxZVU5ZDBYY1UtMW5lbTNFb3pTUjBrV3pnWlV0WWJBNGg4YWlxRzlCSDVRZF9jZzBlYzJ3S3o3WWVLRi10QzhLdFFTY2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
@@ -8669,44 +8669,44 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>12/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>12/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8728,19 +8728,19 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,19 +8772,19 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8794,63 +8794,63 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>CMOC | Investimentos socioambientais somaram quase R$ 14 milhões em 2025 - Brasil Mineral</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNNllOeHNGcldnbTlPcnJhb09pVWRYc3dmcWNhWWlZUkx4Rm9PRkQ4SmQ4M04wUFJGZE13V1BJR01xQ0hVcHVxdlpOSzJKSHR2LUNLSjZETHBhTy1yTkhkZ0hPUmJDSHF3SjNMV0VMV1R5QnhkZm90SjlBNFRJZWVUSWhEb3FJc2Y3Vi1JbDZHZFFXRGVqWEhtaU9JZEVncHlCR0dGajZONXpUdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - portalarauto.com.br</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8889,12 +8889,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
@@ -8916,17 +8916,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Movimento Econômico</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQanphVHkycWR3c05tQ1VBYkl5b3pncV9sRGlGVmJvLVpOUUZRcWRvOFdXc1hhSVFqbDBZMlFNSEdVcnNCVGppQ2ZGMVl5WFN5SUJNWS1FLUVuRUpPRFh3VFZHdk54TndBaU4yZW0zQ3dVeWN3MWpFZTVpRUZudm81MlZTa1NoV2hxSWNxLWltS1piVXJwU3QzdXd2emZWa0RHeDVSV0FNWWhIbzdFeGFycTJjdXIwVm1hZkw5ZGNsazczaURkV0cxek9aQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
@@ -8955,44 +8955,44 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>04/03/2026 10:02</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9004,29 +9004,29 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>04/03/2026 10:02</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9058,51 +9058,51 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Produtores de ureia do Oriente Médio seguram oferta em meio à guerra no Irã - Globo Rural</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOT0xmQU1XdUV0MFAxYW5SVnY1N2lOMDZlOFY1LWZKN09NSE9nS0EyUUVvYmZ4dERnZVI3OWlxeEt3aldwaHNaZ0VMNUtrb3dqWjZ0SEl0M2k3WnRYS055RFBmRm5HN1EtQmFoNE1uQThKcWFiM2V5end2aGtWUGJYeXdPX0VCU0prZE9KYWE3TVpFM3BnOG9MaENaOUNQc2ozVnVkWlRvV0JJTGEzdXhlUkFXMVlwMEwxampxdTlOdkNsclpGMnBJQzRnVVc2V3PSAd4BQVVfeXFMTzlHTHRVNzBueXBMWEl0a0lTM1NfN3YwTkRoM3Y0ZXR2OENJbm90ak5zQ2ZmT05rYWVOOE5mYjZJZ2hwRXJkaTVqcXNMckVwVG1rX21NTS05OFNlY0hDSE1VNUlZY1YtYl9oTFZTZm1mdDhqZkgtVXl3c2JFYjlHbm50cHNXLWhjT05XN1FpMnRidTJzQlRCOHpTbm1kYVlnSVBXU3J1dlB0TFFudzlFcjc5TGM2UF9TTlM4azUwMEFmYlNkTERadUY2b2Q1ckFWNDhacGlvWjJSZWdMM0xn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9131,88 +9131,88 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9263,44 +9263,44 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9329,88 +9329,88 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - ParaibaOnline</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Grolime brings high-performance benefits for Scottish soils</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>14/02/2026 06:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f9c54f431497f7cfa156c825bb&amp;url=https%3a%2f%2fwww.thescottishfarmer.co.uk%2fnews%2f25845962.grolime-brings-high-performance-benefits-scottish-soils%2f&amp;c=18200927900201231641&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Preços domésticos de enxofre enfraqueceram, enquanto os preços do enxofre portuário permaneceram firmes - Sunsirs</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpUHpyeDNlaGFXZGtXb0JTeV9CaWVmTEpQZ19FWmVIaC1kV0J6amJVUzRZRVFOU1ZIVWhaSEtQSFE5ODZ0SEROYnV2OXVINXJnQXpUZ3JTV0g?oc=5</t>
         </is>
       </c>
     </row>
@@ -9422,39 +9422,39 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Preços domésticos de enxofre enfraqueceram, enquanto os preços do enxofre portuário permaneceram firmes - Sunsirs</t>
+          <t>Domínio mineral chinês — por Márcio Coimbra - Revista Oeste</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>07/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpUHpyeDNlaGFXZGtXb0JTeV9CaWVmTEpQZ19FWmVIaC1kV0J6amJVUzRZRVFOU1ZIVWhaSEtQSFE5ODZ0SEROYnV2OXVINXJnQXpUZ3JTV0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Kc01kVmlWMVlaaThURGlzOGZIWkUtZ1QwZ1RfT0pCa20tdUt4RXdFY1NNNDJFVkstdjc4SDVLR3VnRS1zWF9OOVdlQW1kVWZGblJOdXFuMHVnMGVyNEdfVnZuUlhhZ2hV?oc=5</t>
         </is>
       </c>
     </row>
@@ -9466,17 +9466,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
@@ -9488,17 +9488,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Domínio mineral chinês — por Márcio Coimbra - Revista Oeste</t>
+          <t>Ações da Equinox Gold caem quase 10% após CBPM contestar venda de operações na Bahia - MundoBA</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>07/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Kc01kVmlWMVlaaThURGlzOGZIWkUtZ1QwZ1RfT0pCa20tdUt4RXdFY1NNNDJFVkstdjc4SDVLR3VnRS1zWF9OOVdlQW1kVWZGblJOdXFuMHVnMGVyNEdfVnZuUlhhZ2hV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMFU0djRndUxwdzhrVXI3OVdVamZ6YTlWQVowbGhaSlJzLTUyaWl1SFBkTGFNWUd4R0hDTTJhRVZiajNWSFBCeFBGcTd0aGxyMVpkN1djZkJWWDU0NTV0ZnpfX2xCZ2lDQWZwT3pKa29qOG9qZUFDdjl0U0Q3WTVNR19wcnJFVWc4WWFCZXdkZ1VMZUl1RnBldVN1ekh2QXJOSFdGd3dJRDlMWnAxWUY0NjdDRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9510,61 +9510,61 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Ações da Equinox Gold caem quase 10% após CBPM contestar venda de operações na Bahia - MundoBA</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMFU0djRndUxwdzhrVXI3OVdVamZ6YTlWQVowbGhaSlJzLTUyaWl1SFBkTGFNWUd4R0hDTTJhRVZiajNWSFBCeFBGcTd0aGxyMVpkN1djZkJWWDU0NTV0ZnpfX2xCZ2lDQWZwT3pKa29qOG9qZUFDdjl0U0Q3WTVNR19wcnJFVWc4WWFCZXdkZ1VMZUl1RnBldVN1ekh2QXJOSFdGd3dJRDlMWnAxWUY0NjdDRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9576,117 +9576,117 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9696,73 +9696,73 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Rio Doce oferece análise de solo gratuita para fomentar a produtividade e sustentabilidade no campo - Jornal Panorama Minas</t>
+          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>25/01/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQVENaMzhzbm5GOUR3UFBNU2Y5RDNlU2ppUmhXZW9GVnE1NWNxanpBS0Z6S2xrc2Y0eUh4UmFURExNeFBTc2VscUUtSi0tZkRLQ0haeUpfcTlUNV9KZ0VUZXMwZ0phYXNPVU5zcWRiRTdrZlJSQllRLUx5MzE0dktrRjZwX1RKYWg0VmtaSmVYQ2NpM0I3Mi1NZ0FJQk8zMzYxcWdxWDNiOENKN18yVTczTE9PeFY4bEl1MmhxdDdOX1FEaXM1cTQyeEk4dVkxbm43?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,83 +9774,83 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>25/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9862,83 +9862,83 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>11/01/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
+          <t>Venezuela exporta ureia ao Brasil, mas tem pouca relevância no mercado global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>11/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQjJYX29TcVl2MkpsY0EtTDh6VDc3RFlPZGg3WkdjSG9ab0FkeVJKT2x0YllVY2xTbl9xendfSUtGV2RsVmprSzFVZEhURTV0ZmFUMXVRVm5NRXdHaFVJM2VjN1JGaE42VFdnUlhuWlNxdXgwZ3p4YXRycFF0Y0Y2elBtY25RTmQ5eUhFa3ZCcElVbkItWGtnaFlDMjRXU0V5V1ROdjJ0OEhRNTllLXp0cnlHNG52WFBCVjVBMFJvcktUR3E1OERlT0t4b082WUJsQlRfSW1OLUgyTVZwN2Nv0gHkAUFVX3lxTFB2emJXNjY4cTRrZllISFlJbzV1d2g3bzhqWDY0Y18tbGM0c2VMcjdmaDUxZXdLaVh4RkZmdS05MFBxNTQySlNoWnlGTmNna2hlSXBiYlBhTmV2ZElkMi1MNE5rMThGd2FpSEpvQlU4MkU5SFdjV0p5aWVLd1lUbXNqUnotdElHVFVQemtnNmZIbTVvcVVVQV9nTFBoeEMxeHY4ZkI3RlBRWEJPOVhLazhGdk1iR3I5RTE2d2lqZE5OcmdSdmlqR1g2alVUZHVXOHVhUkZvdkZQczJDOXNsRkw4UHZsbA?oc=5</t>
         </is>
       </c>
     </row>
@@ -9950,127 +9950,127 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Venezuela exporta ureia ao Brasil, mas tem pouca relevância no mercado global - Notícias Agrícolas</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOQjJYX29TcVl2MkpsY0EtTDh6VDc3RFlPZGg3WkdjSG9ab0FkeVJKT2x0YllVY2xTbl9xendfSUtGV2RsVmprSzFVZEhURTV0ZmFUMXVRVm5NRXdHaFVJM2VjN1JGaE42VFdnUlhuWlNxdXgwZ3p4YXRycFF0Y0Y2elBtY25RTmQ5eUhFa3ZCcElVbkItWGtnaFlDMjRXU0V5V1ROdjJ0OEhRNTllLXp0cnlHNG52WFBCVjVBMFJvcktUR3E1OERlT0t4b082WUJsQlRfSW1OLUgyTVZwN2Nv0gHkAUFVX3lxTFB2emJXNjY4cTRrZllISFlJbzV1d2g3bzhqWDY0Y18tbGM0c2VMcjdmaDUxZXdLaVh4RkZmdS05MFBxNTQySlNoWnlGTmNna2hlSXBiYlBhTmV2ZElkMi1MNE5rMThGd2FpSEpvQlU4MkU5SFdjV0p5aWVLd1lUbXNqUnotdElHVFVQemtnNmZIbTVvcVVVQV9nTFBoeEMxeHY4ZkI3RlBRWEJPOVhLazhGdk1iR3I5RTE2d2lqZE5OcmdSdmlqR1g2alVUZHVXOHVhUkZvdkZQczJDOXNsRkw4UHZsbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10170,39 +10170,39 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10246,19 +10246,19 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,29 +10290,29 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,17 +10324,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,17 +10544,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,17 +10566,17 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,205 +10588,205 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>12/12/2025 05:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab2a48a4a969f7eaa51f2defde0&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>12/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f9c54f431497f7cfa156c825bb&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>27/11/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>27/11/2025 05:00</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10808,17 +10808,17 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>18/11/2025 05:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10830,479 +10830,479 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab1f71e48cda3bbf137739e5fd4&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>18/11/2025 05:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>10/11/2025 05:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>10/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab2a48a4a969f7eaa51f2defde0&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>17/10/2025 04:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f9c54f431497f7cfa156c825bb&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>O composto. Fundamental para a captura de carbono no solo - vozdocampo.pt</t>
+          <t>Sibelco prioriza ambiente e sustentabilidade - O Mirante</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>17/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5xMkJkQi05dzl4R3RabU44d0U0NnB1cmE3ZTBUQkpjTWJaVTB5c2VpVE0yUEV5VmQ1NkIySE9ma1FBdFE5NTRyRVpIRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcTZuY1FkWnluSllYNDRFMDcyeUtDeHlFeGNSQ0FaV20tcnNreHpHT1NVRUR0ZUd0a0hUOEw0M0EtS3lnd3lTalJrbWI0Q2ZpeUZIWlc0N1VwQ3NrMHhnR1NQV2FEdkp5RVBraXdSMzdoUEpTcEwwVmljdVBRcTF2RzY5azRkQTVhTnZKRDNrQlY5cjlocDlhSWNQQkY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Sibelco prioriza ambiente e sustentabilidade - O Mirante</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcTZuY1FkWnluSllYNDRFMDcyeUtDeHlFeGNSQ0FaV20tcnNreHpHT1NVRUR0ZUd0a0hUOEw0M0EtS3lnd3lTalJrbWI0Q2ZpeUZIWlc0N1VwQ3NrMHhnR1NQV2FEdkp5RVBraXdSMzdoUEpTcEwwVmljdVBRcTF2RzY5azRkQTVhTnZKRDNrQlY5cjlocDlhSWNQQkY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Calcário: o insumo que transformou o Cerrado em uma das maiores potências agrícolas do país</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>09/10/2025 23:34</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faaafb456415c83d37b2a04d41a57&amp;url=https%3a%2f%2fopopular.com.br%2finfomercial%2fcalcario-o-insumo-que-transformou-o-cerrado-em-uma-das-maiores-potencias-agricolas-do-pais-1.3322503&amp;c=8695352406975221608&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Calcário: o insumo que transformou o Cerrado em uma das maiores potências agrícolas do país</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>09/10/2025 23:34</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f5841a4e638039357d1d632668&amp;url=https%3a%2f%2fopopular.com.br%2finfomercial%2fcalcario-o-insumo-que-transformou-o-cerrado-em-uma-das-maiores-potencias-agricolas-do-pais-1.3322503&amp;c=8695352406975221608&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab1f71e48cda3bbf137739e5fd4&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11314,39 +11314,39 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Líder em fornecimento de calcário agrícola, FIDA projeta crescimento do setor na Expointer - Jornal O Sul</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>06/09/2025 04:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRG9EYmVPQVF4emNrdE05dG1YU2dmc29CRnNicHdrWWdfQURremhXQnY1V0FTMW1FX3RfWjVIRlV6cFF4U2FCV3BfR2RJZkc0aGVsTXlBRkZqMnFyY2NNQTZFOGxxZDBFeEx2NUlIa0xYYURuMzM4OWdLWngtZnJYajNncGlpbmdSRGJrZTlibEpyMXh2Nlc2NW1SYjQ3Vnk2TXJ0Z2lBaU90dmRkbTRvcTIyYmjSAboBQVVfeXFMTXUwUXpMVFlNSlFLSkhpUTdBMWdGN2IwUUtyZ05YbTY0R1hvNS1ybkJsdnN2RTJwa0cxQzFCYVVBTU8ySkVLYzRSYWpuS3kyMTV0dnA4b2ZoazFmWUpYWjJWdkFrWFl0QkVKMGpDQlZLM09PM01xZVJGMDgtY0NGN01GdUo2ZEFSM0MweXczVnhielRfbnFLRFN2Zlo3WDc5bE5rTkFlNTk2TVB1QXdhdzgyTTBETk4wNWF3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
@@ -11358,171 +11358,171 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Líder em fornecimento de calcário agrícola, FIDA projeta crescimento do setor na Expointer - Jornal O Sul</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>06/09/2025 04:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRG9EYmVPQVF4emNrdE05dG1YU2dmc29CRnNicHdrWWdfQURremhXQnY1V0FTMW1FX3RfWjVIRlV6cFF4U2FCV3BfR2RJZkc0aGVsTXlBRkZqMnFyY2NNQTZFOGxxZDBFeEx2NUlIa0xYYURuMzM4OWdLWngtZnJYajNncGlpbmdSRGJrZTlibEpyMXh2Nlc2NW1SYjQ3Vnk2TXJ0Z2lBaU90dmRkbTRvcTIyYmjSAboBQVVfeXFMTXUwUXpMVFlNSlFLSkhpUTdBMWdGN2IwUUtyZ05YbTY0R1hvNS1ybkJsdnN2RTJwa0cxQzFCYVVBTU8ySkVLYzRSYWpuS3kyMTV0dnA4b2ZoazFmWUpYWjJWdkFrWFl0QkVKMGpDQlZLM09PM01xZVJGMDgtY0NGN01GdUo2ZEFSM0MweXczVnhielRfbnFLRFN2Zlo3WDc5bE5rTkFlNTk2TVB1QXdhdzgyTTBETk4wNWF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f88ca84a178c4e127f7da09f79&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>26/08/2025 04:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>19/08/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>26/08/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5faab2a48a4a969f7eaa51f2defde0&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>22/08/2025 04:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11534,83 +11534,83 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>19/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Primeira-dama entrega computadores e anuncia bioindústria para marisqueiras de Itapissuma - Diario de Pernambuco</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>12/08/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5f87f9c54f431497f7cfa156c825bb&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPZEk2U0pCazdlWnVLR1lqQ1NYWEVxNTJ3Z3M2TlphU0ZmdDVzb09XTGx2cmN3SE81QngtYVZ0R2xubFJvTzV4dFJrUjlUeDNkbF9ZcEtmbjVSLUJoX3dEWVpIUlFGSmtzbkFVXzJaZi1KSEd4Y1FHVFh5czM5c1NLWjFrM3piWjdhVUxBRFFSQmRJMGpRdWp3SERFYnI3cENKM2I2VERjcXh0RlVaNzZwX2ExMUkyR19GZk4tRU45Zl9PODdQaDdnYnhtb3JZajJ5OERNWkhxaUo0aFRoZDNwc1phUmlsMzM4QnpYa3ZOclhMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>06/08/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11622,17 +11622,17 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Primeira-dama entrega computadores e anuncia bioindústria para marisqueiras de Itapissuma - Diario de Pernambuco</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>12/08/2025 04:00</t>
+          <t>02/08/2025 04:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPZEk2U0pCazdlWnVLR1lqQ1NYWEVxNTJ3Z3M2TlphU0ZmdDVzb09XTGx2cmN3SE81QngtYVZ0R2xubFJvTzV4dFJrUjlUeDNkbF9ZcEtmbjVSLUJoX3dEWVpIUlFGSmtzbkFVXzJaZi1KSEd4Y1FHVFh5czM5c1NLWjFrM3piWjdhVUxBRFFSQmRJMGpRdWp3SERFYnI3cENKM2I2VERjcXh0RlVaNzZwX2ExMUkyR19GZk4tRU45Zl9PODdQaDdnYnhtb3JZajJ5OERNWkhxaUo0aFRoZDNwc1phUmlsMzM4QnpYa3ZOclhMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
@@ -11644,125 +11644,59 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>11/08/2025 04:00</t>
+          <t>01/08/2025 21:12</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>06/08/2025 04:00</t>
+          <t>31/07/2025 04:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>02/08/2025 04:00</t>
+          <t>29/07/2025 04:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>limestone</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>01/08/2025 21:12</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>corretivo de solo</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>31/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>CMOC</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>29/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
